--- a/research/traditional_assets/database/data/south_africa/south_africa_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_cable_tv.xlsx
@@ -1275,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1412,22 +1412,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09521466873111471</v>
+        <v>0.09499043912554071</v>
       </c>
       <c r="C2">
-        <v>3718.425001725433</v>
+        <v>3692.714910519662</v>
       </c>
       <c r="D2">
-        <v>3386.525001725433</v>
+        <v>3397.926333167828</v>
       </c>
       <c r="E2">
-        <v>-1255.642264816686</v>
+        <v>-1218.530842168519</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>37.11142264816686</v>
       </c>
       <c r="G2">
         <v>331.9</v>
@@ -1448,28 +1448,28 @@
         <v>430.3775</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.866704559202793</v>
       </c>
       <c r="N2">
-        <v>430.3775</v>
+        <v>428.5107954407972</v>
       </c>
       <c r="O2">
-        <v>116.201925</v>
+        <v>115.6979147690153</v>
       </c>
       <c r="P2">
-        <v>314.175575</v>
+        <v>312.812880671782</v>
       </c>
       <c r="Q2">
-        <v>361.2755749999999</v>
+        <v>359.9128806717819</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09521466873111471</v>
+        <v>0.0955790395207482</v>
       </c>
       <c r="T2">
-        <v>0.5919749984509941</v>
+        <v>0.5963400666213904</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>230.554694838159</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1494,22 +1494,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09499043912554071</v>
+        <v>0.0947662095199667</v>
       </c>
       <c r="C3">
-        <v>3692.714910519662</v>
+        <v>3667.081847814982</v>
       </c>
       <c r="D3">
-        <v>3397.926333167828</v>
+        <v>3409.404693111315</v>
       </c>
       <c r="E3">
-        <v>-1218.530842168519</v>
+        <v>-1181.419419520352</v>
       </c>
       <c r="F3">
-        <v>37.11142264816686</v>
+        <v>74.22284529633372</v>
       </c>
       <c r="G3">
         <v>331.9</v>
@@ -1530,28 +1530,28 @@
         <v>430.3775</v>
       </c>
       <c r="M3">
-        <v>1.866704559202793</v>
+        <v>3.733409118405586</v>
       </c>
       <c r="N3">
-        <v>428.5107954407972</v>
+        <v>426.6440908815944</v>
       </c>
       <c r="O3">
-        <v>115.6979147690153</v>
+        <v>115.1939045380305</v>
       </c>
       <c r="P3">
-        <v>312.812880671782</v>
+        <v>311.4501863435639</v>
       </c>
       <c r="Q3">
-        <v>359.9128806717819</v>
+        <v>358.5501863435639</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0955790395207482</v>
+        <v>0.09595084644894561</v>
       </c>
       <c r="T3">
-        <v>0.5963400666213904</v>
+        <v>0.6007942178156722</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>230.554694838159</v>
+        <v>115.2773474190795</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,22 +1576,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0947662095199667</v>
+        <v>0.09454197991439267</v>
       </c>
       <c r="C4">
-        <v>3667.081847814982</v>
+        <v>3641.526596875334</v>
       </c>
       <c r="D4">
-        <v>3409.404693111315</v>
+        <v>3420.960864819835</v>
       </c>
       <c r="E4">
-        <v>-1181.419419520352</v>
+        <v>-1144.307996872185</v>
       </c>
       <c r="F4">
-        <v>74.22284529633372</v>
+        <v>111.3342679445006</v>
       </c>
       <c r="G4">
         <v>331.9</v>
@@ -1612,28 +1612,28 @@
         <v>430.3775</v>
       </c>
       <c r="M4">
-        <v>3.733409118405586</v>
+        <v>5.600113677608378</v>
       </c>
       <c r="N4">
-        <v>426.6440908815944</v>
+        <v>424.7773863223916</v>
       </c>
       <c r="O4">
-        <v>115.1939045380305</v>
+        <v>114.6898943070457</v>
       </c>
       <c r="P4">
-        <v>311.4501863435639</v>
+        <v>310.0874920153459</v>
       </c>
       <c r="Q4">
-        <v>358.5501863435639</v>
+        <v>357.1874920153459</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09595084644894561</v>
+        <v>0.0963303194993739</v>
       </c>
       <c r="T4">
-        <v>0.6007942178156722</v>
+        <v>0.6053402071789084</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>115.2773474190795</v>
+        <v>76.85156494605302</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,22 +1658,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09454197991439267</v>
+        <v>0.09431775030881868</v>
       </c>
       <c r="C5">
-        <v>3641.526596875334</v>
+        <v>3616.049951620261</v>
       </c>
       <c r="D5">
-        <v>3420.960864819835</v>
+        <v>3432.595642212928</v>
       </c>
       <c r="E5">
-        <v>-1144.307996872185</v>
+        <v>-1107.196574224018</v>
       </c>
       <c r="F5">
-        <v>111.3342679445006</v>
+        <v>148.4456905926674</v>
       </c>
       <c r="G5">
         <v>331.9</v>
@@ -1694,28 +1694,28 @@
         <v>430.3775</v>
       </c>
       <c r="M5">
-        <v>5.600113677608378</v>
+        <v>7.466818236811172</v>
       </c>
       <c r="N5">
-        <v>424.7773863223916</v>
+        <v>422.9106817631888</v>
       </c>
       <c r="O5">
-        <v>114.6898943070457</v>
+        <v>114.185884076061</v>
       </c>
       <c r="P5">
-        <v>310.0874920153459</v>
+        <v>308.7247976871279</v>
       </c>
       <c r="Q5">
-        <v>357.1874920153459</v>
+        <v>355.8247976871278</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0963303194993739</v>
+        <v>0.0967176982383528</v>
       </c>
       <c r="T5">
-        <v>0.6053402071789084</v>
+        <v>0.6099809046538786</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>76.85156494605302</v>
+        <v>57.63867370953975</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,22 +1740,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09431775030881868</v>
+        <v>0.09409352070324466</v>
       </c>
       <c r="C6">
-        <v>3616.049951620261</v>
+        <v>3590.652716806736</v>
       </c>
       <c r="D6">
-        <v>3432.595642212928</v>
+        <v>3444.30983004757</v>
       </c>
       <c r="E6">
-        <v>-1107.196574224018</v>
+        <v>-1070.085151575851</v>
       </c>
       <c r="F6">
-        <v>148.4456905926674</v>
+        <v>185.5571132408343</v>
       </c>
       <c r="G6">
         <v>331.9</v>
@@ -1776,28 +1776,28 @@
         <v>430.3775</v>
       </c>
       <c r="M6">
-        <v>7.466818236811172</v>
+        <v>9.333522796013963</v>
       </c>
       <c r="N6">
-        <v>422.9106817631888</v>
+        <v>421.0439772039861</v>
       </c>
       <c r="O6">
-        <v>114.185884076061</v>
+        <v>113.6818738450762</v>
       </c>
       <c r="P6">
-        <v>308.7247976871279</v>
+        <v>307.3621033589098</v>
       </c>
       <c r="Q6">
-        <v>355.8247976871278</v>
+        <v>354.4621033589098</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0967176982383528</v>
+        <v>0.09711323231920491</v>
       </c>
       <c r="T6">
-        <v>0.6099809046538786</v>
+        <v>0.6147193010230586</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>57.63867370953975</v>
+        <v>46.11093896763181</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,22 +1822,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09409352070324466</v>
+        <v>0.09386929109767067</v>
       </c>
       <c r="C7">
-        <v>3590.652716806736</v>
+        <v>3565.335708214699</v>
       </c>
       <c r="D7">
-        <v>3444.30983004757</v>
+        <v>3456.1042441037</v>
       </c>
       <c r="E7">
-        <v>-1070.085151575851</v>
+        <v>-1032.973728927685</v>
       </c>
       <c r="F7">
-        <v>185.5571132408343</v>
+        <v>222.6685358890011</v>
       </c>
       <c r="G7">
         <v>331.9</v>
@@ -1858,28 +1858,28 @@
         <v>430.3775</v>
       </c>
       <c r="M7">
-        <v>9.333522796013963</v>
+        <v>11.20022735521676</v>
       </c>
       <c r="N7">
-        <v>421.0439772039861</v>
+        <v>419.1772726447832</v>
       </c>
       <c r="O7">
-        <v>113.6818738450762</v>
+        <v>113.1778636140915</v>
       </c>
       <c r="P7">
-        <v>307.3621033589098</v>
+        <v>305.9994090306917</v>
       </c>
       <c r="Q7">
-        <v>354.4621033589098</v>
+        <v>353.0994090306917</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09711323231920491</v>
+        <v>0.09751718201879858</v>
       </c>
       <c r="T7">
-        <v>0.6147193010230586</v>
+        <v>0.6195585143362639</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>46.11093896763181</v>
+        <v>38.42578247302649</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,22 +1904,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09386929109767067</v>
+        <v>0.09364506149209666</v>
       </c>
       <c r="C8">
-        <v>3565.335708214699</v>
+        <v>3540.099752836454</v>
       </c>
       <c r="D8">
-        <v>3456.1042441037</v>
+        <v>3467.979711373622</v>
       </c>
       <c r="E8">
-        <v>-1032.973728927685</v>
+        <v>-995.8623062795177</v>
       </c>
       <c r="F8">
-        <v>222.6685358890011</v>
+        <v>259.7799585371679</v>
       </c>
       <c r="G8">
         <v>331.9</v>
@@ -1940,28 +1940,28 @@
         <v>430.3775</v>
       </c>
       <c r="M8">
-        <v>11.20022735521676</v>
+        <v>13.06693191441955</v>
       </c>
       <c r="N8">
-        <v>419.1772726447832</v>
+        <v>417.3105680855804</v>
       </c>
       <c r="O8">
-        <v>113.1778636140915</v>
+        <v>112.6738533831067</v>
       </c>
       <c r="P8">
-        <v>305.9994090306917</v>
+        <v>304.6367147024737</v>
       </c>
       <c r="Q8">
-        <v>353.0994090306917</v>
+        <v>351.7367147024736</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09751718201879858</v>
+        <v>0.09792981880870608</v>
       </c>
       <c r="T8">
-        <v>0.6195585143362639</v>
+        <v>0.6245017967529788</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.4257824730265</v>
+        <v>32.93638497687986</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,22 +1986,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09364506149209664</v>
+        <v>0.09342083188652264</v>
       </c>
       <c r="C9">
-        <v>3540.099752836455</v>
+        <v>3514.945689069956</v>
       </c>
       <c r="D9">
-        <v>3467.979711373623</v>
+        <v>3479.937070255291</v>
       </c>
       <c r="E9">
-        <v>-995.8623062795176</v>
+        <v>-958.7508836313507</v>
       </c>
       <c r="F9">
-        <v>259.779958537168</v>
+        <v>296.8913811853349</v>
       </c>
       <c r="G9">
         <v>331.9</v>
@@ -2022,28 +2022,28 @@
         <v>430.3775</v>
       </c>
       <c r="M9">
-        <v>13.06693191441955</v>
+        <v>14.93363647362234</v>
       </c>
       <c r="N9">
-        <v>417.3105680855804</v>
+        <v>415.4438635263776</v>
       </c>
       <c r="O9">
-        <v>112.6738533831067</v>
+        <v>112.169843152122</v>
       </c>
       <c r="P9">
-        <v>304.6367147024737</v>
+        <v>303.2740203742557</v>
       </c>
       <c r="Q9">
-        <v>351.7367147024736</v>
+        <v>350.3740203742556</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09792981880870608</v>
+        <v>0.09835142596361157</v>
       </c>
       <c r="T9">
-        <v>0.6245017967529788</v>
+        <v>0.6295525418309268</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.93638497687985</v>
+        <v>28.81933685476987</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,22 +2068,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09342083188652264</v>
+        <v>0.09319660228094864</v>
       </c>
       <c r="C10">
-        <v>3514.945689069956</v>
+        <v>3489.874366916122</v>
       </c>
       <c r="D10">
-        <v>3479.937070255291</v>
+        <v>3491.977170749623</v>
       </c>
       <c r="E10">
-        <v>-958.7508836313507</v>
+        <v>-921.6394609831839</v>
       </c>
       <c r="F10">
-        <v>296.8913811853349</v>
+        <v>334.0028038335017</v>
       </c>
       <c r="G10">
         <v>331.9</v>
@@ -2104,28 +2104,28 @@
         <v>430.3775</v>
       </c>
       <c r="M10">
-        <v>14.93363647362234</v>
+        <v>16.80034103282513</v>
       </c>
       <c r="N10">
-        <v>415.4438635263776</v>
+        <v>413.5771589671749</v>
       </c>
       <c r="O10">
-        <v>112.169843152122</v>
+        <v>111.6658329211372</v>
       </c>
       <c r="P10">
-        <v>303.2740203742557</v>
+        <v>301.9113260460376</v>
       </c>
       <c r="Q10">
-        <v>350.3740203742556</v>
+        <v>349.0113260460376</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09835142596361157</v>
+        <v>0.09878229920983367</v>
       </c>
       <c r="T10">
-        <v>0.6295525418309268</v>
+        <v>0.6347142922952033</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.81933685476987</v>
+        <v>25.617188315351</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,22 +2150,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09319660228094864</v>
+        <v>0.09297237267537463</v>
       </c>
       <c r="C11">
-        <v>3489.874366916122</v>
+        <v>3464.886648180254</v>
       </c>
       <c r="D11">
-        <v>3491.977170749623</v>
+        <v>3504.100874661923</v>
       </c>
       <c r="E11">
-        <v>-921.6394609831839</v>
+        <v>-884.5280383350171</v>
       </c>
       <c r="F11">
-        <v>334.0028038335017</v>
+        <v>371.1142264816685</v>
       </c>
       <c r="G11">
         <v>331.9</v>
@@ -2186,28 +2186,28 @@
         <v>430.3775</v>
       </c>
       <c r="M11">
-        <v>16.80034103282513</v>
+        <v>18.66704559202793</v>
       </c>
       <c r="N11">
-        <v>413.5771589671749</v>
+        <v>411.7104544079721</v>
       </c>
       <c r="O11">
-        <v>111.6658329211372</v>
+        <v>111.1618226901525</v>
       </c>
       <c r="P11">
-        <v>301.9113260460376</v>
+        <v>300.5486317178196</v>
       </c>
       <c r="Q11">
-        <v>349.0113260460376</v>
+        <v>347.6486317178196</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09878229920983367</v>
+        <v>0.09922274741708291</v>
       </c>
       <c r="T11">
-        <v>0.6347142922952033</v>
+        <v>0.6399907483253525</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.617188315351</v>
+        <v>23.0554694838159</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,22 +2232,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09297237267537463</v>
+        <v>0.0927481430698006</v>
       </c>
       <c r="C12">
-        <v>3464.886648180254</v>
+        <v>3439.98340667767</v>
       </c>
       <c r="D12">
-        <v>3504.100874661923</v>
+        <v>3516.309055807506</v>
       </c>
       <c r="E12">
-        <v>-884.5280383350171</v>
+        <v>-847.4166156868503</v>
       </c>
       <c r="F12">
-        <v>371.1142264816685</v>
+        <v>408.2256491298354</v>
       </c>
       <c r="G12">
         <v>331.9</v>
@@ -2268,28 +2268,28 @@
         <v>430.3775</v>
       </c>
       <c r="M12">
-        <v>18.66704559202793</v>
+        <v>20.53375015123072</v>
       </c>
       <c r="N12">
-        <v>411.7104544079721</v>
+        <v>409.8437498487693</v>
       </c>
       <c r="O12">
-        <v>111.1618226901525</v>
+        <v>110.6578124591677</v>
       </c>
       <c r="P12">
-        <v>300.5486317178196</v>
+        <v>299.1859373896016</v>
       </c>
       <c r="Q12">
-        <v>347.6486317178196</v>
+        <v>346.2859373896015</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09922274741708291</v>
+        <v>0.09967309333685462</v>
       </c>
       <c r="T12">
-        <v>0.6399907483253525</v>
+        <v>0.6453857764011232</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.0554694838159</v>
+        <v>20.95951771255991</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,22 +2314,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0927481430698006</v>
+        <v>0.0925239134642266</v>
       </c>
       <c r="C13">
-        <v>3439.98340667767</v>
+        <v>3415.165528443642</v>
       </c>
       <c r="D13">
-        <v>3516.309055807506</v>
+        <v>3528.602600221644</v>
       </c>
       <c r="E13">
-        <v>-847.4166156868503</v>
+        <v>-810.3051930386835</v>
       </c>
       <c r="F13">
-        <v>408.2256491298354</v>
+        <v>445.3370717780022</v>
       </c>
       <c r="G13">
         <v>331.9</v>
@@ -2350,28 +2350,28 @@
         <v>430.3775</v>
       </c>
       <c r="M13">
-        <v>20.53375015123072</v>
+        <v>22.40045471043351</v>
       </c>
       <c r="N13">
-        <v>409.8437498487693</v>
+        <v>407.9770452895665</v>
       </c>
       <c r="O13">
-        <v>110.6578124591677</v>
+        <v>110.153802228183</v>
       </c>
       <c r="P13">
-        <v>299.1859373896016</v>
+        <v>297.8232430613836</v>
       </c>
       <c r="Q13">
-        <v>346.2859373896015</v>
+        <v>344.9232430613835</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09967309333685462</v>
+        <v>0.1001336743911666</v>
       </c>
       <c r="T13">
-        <v>0.6453857764011232</v>
+        <v>0.6509034187513431</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.95951771255991</v>
+        <v>19.21289123651325</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,22 +2396,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0925239134642266</v>
+        <v>0.09229968385865259</v>
       </c>
       <c r="C14">
-        <v>3415.165528443642</v>
+        <v>3390.433911947765</v>
       </c>
       <c r="D14">
-        <v>3528.602600221644</v>
+        <v>3540.982406373934</v>
       </c>
       <c r="E14">
-        <v>-810.3051930386835</v>
+        <v>-773.1937703905164</v>
       </c>
       <c r="F14">
-        <v>445.3370717780022</v>
+        <v>482.4484944261691</v>
       </c>
       <c r="G14">
         <v>331.9</v>
@@ -2432,28 +2432,28 @@
         <v>430.3775</v>
       </c>
       <c r="M14">
-        <v>22.40045471043351</v>
+        <v>24.26715926963631</v>
       </c>
       <c r="N14">
-        <v>407.9770452895665</v>
+        <v>406.1103407303637</v>
       </c>
       <c r="O14">
-        <v>110.153802228183</v>
+        <v>109.6497919971982</v>
       </c>
       <c r="P14">
-        <v>297.8232430613836</v>
+        <v>296.4605487331655</v>
       </c>
       <c r="Q14">
-        <v>344.9232430613835</v>
+        <v>343.5605487331655</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1001336743911666</v>
+        <v>0.1006048435156926</v>
       </c>
       <c r="T14">
-        <v>0.6509034187513431</v>
+        <v>0.6565479034544416</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.21289123651325</v>
+        <v>17.73497652601223</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,22 +2478,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09229968385865259</v>
+        <v>0.09207545425307859</v>
       </c>
       <c r="C15">
-        <v>3390.433911947765</v>
+        <v>3365.789468312849</v>
       </c>
       <c r="D15">
-        <v>3540.982406373934</v>
+        <v>3553.449385387185</v>
       </c>
       <c r="E15">
-        <v>-773.1937703905164</v>
+        <v>-736.0823477423496</v>
       </c>
       <c r="F15">
-        <v>482.4484944261691</v>
+        <v>519.559917074336</v>
       </c>
       <c r="G15">
         <v>331.9</v>
@@ -2514,28 +2514,28 @@
         <v>430.3775</v>
       </c>
       <c r="M15">
-        <v>24.26715926963631</v>
+        <v>26.1338638288391</v>
       </c>
       <c r="N15">
-        <v>406.1103407303637</v>
+        <v>404.2436361711609</v>
       </c>
       <c r="O15">
-        <v>109.6497919971982</v>
+        <v>109.1457817662135</v>
       </c>
       <c r="P15">
-        <v>296.4605487331655</v>
+        <v>295.0978544049474</v>
       </c>
       <c r="Q15">
-        <v>343.5605487331655</v>
+        <v>342.1978544049474</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1006048435156926</v>
+        <v>0.1010869700617193</v>
       </c>
       <c r="T15">
-        <v>0.6565479034544416</v>
+        <v>0.6623236552436588</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.73497652601223</v>
+        <v>16.46819248843993</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,22 +2560,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09207545425307859</v>
+        <v>0.09185122464750456</v>
       </c>
       <c r="C16">
-        <v>3365.789468312849</v>
+        <v>3341.23312153845</v>
       </c>
       <c r="D16">
-        <v>3553.449385387185</v>
+        <v>3566.004461260953</v>
       </c>
       <c r="E16">
-        <v>-736.0823477423496</v>
+        <v>-698.9709250941827</v>
       </c>
       <c r="F16">
-        <v>519.559917074336</v>
+        <v>556.6713397225029</v>
       </c>
       <c r="G16">
         <v>331.9</v>
@@ -2596,28 +2596,28 @@
         <v>430.3775</v>
       </c>
       <c r="M16">
-        <v>26.1338638288391</v>
+        <v>28.00056838804189</v>
       </c>
       <c r="N16">
-        <v>404.2436361711609</v>
+        <v>402.3769316119581</v>
       </c>
       <c r="O16">
-        <v>109.1457817662135</v>
+        <v>108.6417715352287</v>
       </c>
       <c r="P16">
-        <v>295.0978544049474</v>
+        <v>293.7351600767294</v>
       </c>
       <c r="Q16">
-        <v>342.1978544049474</v>
+        <v>340.8351600767294</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1010869700617193</v>
+        <v>0.1015804407617701</v>
       </c>
       <c r="T16">
-        <v>0.6623236552436588</v>
+        <v>0.6682353070749751</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.46819248843993</v>
+        <v>15.3703129892106</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,22 +2642,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09185122464750456</v>
+        <v>0.09162699504193056</v>
       </c>
       <c r="C17">
-        <v>3341.23312153845</v>
+        <v>3316.765808729156</v>
       </c>
       <c r="D17">
-        <v>3566.004461260953</v>
+        <v>3578.648571099825</v>
       </c>
       <c r="E17">
-        <v>-698.9709250941828</v>
+        <v>-661.8595024460159</v>
       </c>
       <c r="F17">
-        <v>556.6713397225028</v>
+        <v>593.7827623706697</v>
       </c>
       <c r="G17">
         <v>331.9</v>
@@ -2678,28 +2678,28 @@
         <v>430.3775</v>
       </c>
       <c r="M17">
-        <v>28.00056838804189</v>
+        <v>29.86727294724469</v>
       </c>
       <c r="N17">
-        <v>402.3769316119581</v>
+        <v>400.5102270527553</v>
       </c>
       <c r="O17">
-        <v>108.6417715352287</v>
+        <v>108.137761304244</v>
       </c>
       <c r="P17">
-        <v>293.7351600767294</v>
+        <v>292.3724657485114</v>
       </c>
       <c r="Q17">
-        <v>340.8351600767294</v>
+        <v>339.4724657485114</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1015804407617701</v>
+        <v>0.1020856607642031</v>
       </c>
       <c r="T17">
-        <v>0.6682353070749751</v>
+        <v>0.6742877125213228</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.3703129892106</v>
+        <v>14.40966842738494</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,22 +2724,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09162699504193056</v>
+        <v>0.09140276543635656</v>
       </c>
       <c r="C18">
-        <v>3316.765808729156</v>
+        <v>3292.388480327748</v>
       </c>
       <c r="D18">
-        <v>3578.648571099825</v>
+        <v>3591.382665346585</v>
       </c>
       <c r="E18">
-        <v>-661.8595024460159</v>
+        <v>-624.7480797978491</v>
       </c>
       <c r="F18">
-        <v>593.7827623706697</v>
+        <v>630.8941850188365</v>
       </c>
       <c r="G18">
         <v>331.9</v>
@@ -2760,28 +2760,28 @@
         <v>430.3775</v>
       </c>
       <c r="M18">
-        <v>29.86727294724469</v>
+        <v>31.73397750644748</v>
       </c>
       <c r="N18">
-        <v>400.5102270527553</v>
+        <v>398.6435224935525</v>
       </c>
       <c r="O18">
-        <v>108.137761304244</v>
+        <v>107.6337510732592</v>
       </c>
       <c r="P18">
-        <v>292.3724657485114</v>
+        <v>291.0097714202933</v>
       </c>
       <c r="Q18">
-        <v>339.4724657485114</v>
+        <v>338.1097714202933</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1020856607642031</v>
+        <v>0.1026030547425983</v>
       </c>
       <c r="T18">
-        <v>0.6742877125213228</v>
+        <v>0.6804859590627632</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.40966842738494</v>
+        <v>13.56204087283288</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,22 +2806,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09140276543635656</v>
+        <v>0.09137563583078252</v>
       </c>
       <c r="C19">
-        <v>3292.388480327748</v>
+        <v>3256.823907787679</v>
       </c>
       <c r="D19">
-        <v>3591.382665346585</v>
+        <v>3592.929515454682</v>
       </c>
       <c r="E19">
-        <v>-624.7480797978491</v>
+        <v>-587.6366571496822</v>
       </c>
       <c r="F19">
-        <v>630.8941850188365</v>
+        <v>668.0056076670035</v>
       </c>
       <c r="G19">
         <v>331.9</v>
@@ -2842,45 +2842,45 @@
         <v>430.3775</v>
       </c>
       <c r="M19">
-        <v>31.73397750644748</v>
+        <v>34.60269047715078</v>
       </c>
       <c r="N19">
-        <v>398.6435224935525</v>
+        <v>395.7748095228492</v>
       </c>
       <c r="O19">
-        <v>107.6337510732592</v>
+        <v>106.8591985711693</v>
       </c>
       <c r="P19">
-        <v>291.0097714202933</v>
+        <v>288.9156109516799</v>
       </c>
       <c r="Q19">
-        <v>338.1097714202933</v>
+        <v>336.0156109516799</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1026030547425983</v>
+        <v>0.1031330680863202</v>
       </c>
       <c r="T19">
-        <v>0.6804859590627632</v>
+        <v>0.6868353823491168</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.27</v>
       </c>
       <c r="W19">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.56204087283288</v>
+        <v>12.43768892144938</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,22 +2888,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09137563583078254</v>
+        <v>0.09116235622520853</v>
       </c>
       <c r="C20">
-        <v>3256.823907787678</v>
+        <v>3231.919630929115</v>
       </c>
       <c r="D20">
-        <v>3592.929515454681</v>
+        <v>3605.136661244285</v>
       </c>
       <c r="E20">
-        <v>-587.6366571496823</v>
+        <v>-550.5252345015153</v>
       </c>
       <c r="F20">
-        <v>668.0056076670033</v>
+        <v>705.1170303151703</v>
       </c>
       <c r="G20">
         <v>331.9</v>
@@ -2924,28 +2924,28 @@
         <v>430.3775</v>
       </c>
       <c r="M20">
-        <v>34.60269047715077</v>
+        <v>36.52506217032582</v>
       </c>
       <c r="N20">
-        <v>395.7748095228492</v>
+        <v>393.8524378296742</v>
       </c>
       <c r="O20">
-        <v>106.8591985711693</v>
+        <v>106.340158214012</v>
       </c>
       <c r="P20">
-        <v>288.9156109516799</v>
+        <v>287.5122796156621</v>
       </c>
       <c r="Q20">
-        <v>336.0156109516799</v>
+        <v>334.6122796156621</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1031330680863202</v>
+        <v>0.1036761681792698</v>
       </c>
       <c r="T20">
-        <v>0.6868353823491168</v>
+        <v>0.6933415815190841</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.43768892144938</v>
+        <v>11.7830737150573</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,22 +2970,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09116235622520853</v>
+        <v>0.09094907661963453</v>
       </c>
       <c r="C21">
-        <v>3231.919630929115</v>
+        <v>3207.098585548977</v>
       </c>
       <c r="D21">
-        <v>3605.136661244285</v>
+        <v>3617.427038512314</v>
       </c>
       <c r="E21">
-        <v>-550.5252345015153</v>
+        <v>-513.4138118533485</v>
       </c>
       <c r="F21">
-        <v>705.1170303151703</v>
+        <v>742.2284529633371</v>
       </c>
       <c r="G21">
         <v>331.9</v>
@@ -3006,28 +3006,28 @@
         <v>430.3775</v>
       </c>
       <c r="M21">
-        <v>36.52506217032582</v>
+        <v>38.44743386350086</v>
       </c>
       <c r="N21">
-        <v>393.8524378296742</v>
+        <v>391.9300661364991</v>
       </c>
       <c r="O21">
-        <v>106.340158214012</v>
+        <v>105.8211178568548</v>
       </c>
       <c r="P21">
-        <v>287.5122796156621</v>
+        <v>286.1089482796444</v>
       </c>
       <c r="Q21">
-        <v>334.6122796156621</v>
+        <v>333.2089482796443</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1036761681792698</v>
+        <v>0.1042328457745432</v>
       </c>
       <c r="T21">
-        <v>0.6933415815190841</v>
+        <v>0.7000104356683006</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.7830737150573</v>
+        <v>11.19392002930444</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,22 +3052,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09094907661963453</v>
+        <v>0.09073579701406051</v>
       </c>
       <c r="C22">
-        <v>3207.098585548977</v>
+        <v>3182.361625799814</v>
       </c>
       <c r="D22">
-        <v>3617.427038512314</v>
+        <v>3629.801501411318</v>
       </c>
       <c r="E22">
-        <v>-513.4138118533485</v>
+        <v>-476.3023892051816</v>
       </c>
       <c r="F22">
-        <v>742.2284529633371</v>
+        <v>779.339875611504</v>
       </c>
       <c r="G22">
         <v>331.9</v>
@@ -3088,28 +3088,28 @@
         <v>430.3775</v>
       </c>
       <c r="M22">
-        <v>38.44743386350086</v>
+        <v>40.36980555667591</v>
       </c>
       <c r="N22">
-        <v>391.9300661364991</v>
+        <v>390.0076944433241</v>
       </c>
       <c r="O22">
-        <v>105.8211178568548</v>
+        <v>105.3020774996975</v>
       </c>
       <c r="P22">
-        <v>286.1089482796444</v>
+        <v>284.7056169436266</v>
       </c>
       <c r="Q22">
-        <v>333.2089482796443</v>
+        <v>331.8056169436265</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1042328457745432</v>
+        <v>0.1048036164734943</v>
       </c>
       <c r="T22">
-        <v>0.7000104356683006</v>
+        <v>0.70684812156813</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.19392002930444</v>
+        <v>10.66087621838518</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,22 +3134,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09073579701406051</v>
+        <v>0.09052251740848649</v>
       </c>
       <c r="C23">
-        <v>3182.361625799814</v>
+        <v>3157.709617561801</v>
       </c>
       <c r="D23">
-        <v>3629.801501411318</v>
+        <v>3642.260915821472</v>
       </c>
       <c r="E23">
-        <v>-476.3023892051817</v>
+        <v>-439.1909665570148</v>
       </c>
       <c r="F23">
-        <v>779.3398756115039</v>
+        <v>816.4512982596708</v>
       </c>
       <c r="G23">
         <v>331.9</v>
@@ -3170,28 +3170,28 @@
         <v>430.3775</v>
       </c>
       <c r="M23">
-        <v>40.3698055566759</v>
+        <v>42.29217724985094</v>
       </c>
       <c r="N23">
-        <v>390.0076944433241</v>
+        <v>388.085322750149</v>
       </c>
       <c r="O23">
-        <v>105.3020774996975</v>
+        <v>104.7830371425403</v>
       </c>
       <c r="P23">
-        <v>284.7056169436266</v>
+        <v>283.3022856076088</v>
       </c>
       <c r="Q23">
-        <v>331.8056169436265</v>
+        <v>330.4022856076087</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1048036164734943</v>
+        <v>0.1053890223185724</v>
       </c>
       <c r="T23">
-        <v>0.70684812156813</v>
+        <v>0.7138611327474423</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.66087621838518</v>
+        <v>10.17629093573131</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,22 +3216,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09052251740848649</v>
+        <v>0.09059466780291249</v>
       </c>
       <c r="C24">
-        <v>3157.709617561801</v>
+        <v>3116.373735105802</v>
       </c>
       <c r="D24">
-        <v>3642.260915821472</v>
+        <v>3638.03645601364</v>
       </c>
       <c r="E24">
-        <v>-439.1909665570148</v>
+        <v>-402.0795439088479</v>
       </c>
       <c r="F24">
-        <v>816.4512982596708</v>
+        <v>853.5627209078377</v>
       </c>
       <c r="G24">
         <v>331.9</v>
@@ -3252,45 +3252,45 @@
         <v>430.3775</v>
       </c>
       <c r="M24">
-        <v>42.29217724985094</v>
+        <v>45.66560556856932</v>
       </c>
       <c r="N24">
-        <v>388.085322750149</v>
+        <v>384.7118944314307</v>
       </c>
       <c r="O24">
-        <v>104.7830371425403</v>
+        <v>103.8722114964863</v>
       </c>
       <c r="P24">
-        <v>283.3022856076088</v>
+        <v>280.8396829349444</v>
       </c>
       <c r="Q24">
-        <v>330.4022856076087</v>
+        <v>327.9396829349444</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1053890223185724</v>
+        <v>0.105989633510276</v>
       </c>
       <c r="T24">
-        <v>0.7138611327474423</v>
+        <v>0.7210563000612823</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.27</v>
       </c>
       <c r="W24">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.17629093573131</v>
+        <v>9.424543803624053</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,22 +3298,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09059466780291249</v>
+        <v>0.09039379819733849</v>
       </c>
       <c r="C25">
-        <v>3116.373735105802</v>
+        <v>3091.047793764216</v>
       </c>
       <c r="D25">
-        <v>3638.03645601364</v>
+        <v>3649.821937320221</v>
       </c>
       <c r="E25">
-        <v>-402.0795439088479</v>
+        <v>-364.9681212606811</v>
       </c>
       <c r="F25">
-        <v>853.5627209078377</v>
+        <v>890.6741435560045</v>
       </c>
       <c r="G25">
         <v>331.9</v>
@@ -3334,28 +3334,28 @@
         <v>430.3775</v>
       </c>
       <c r="M25">
-        <v>45.66560556856932</v>
+        <v>47.65106668024625</v>
       </c>
       <c r="N25">
-        <v>384.7118944314307</v>
+        <v>382.7264333197538</v>
       </c>
       <c r="O25">
-        <v>103.8722114964863</v>
+        <v>103.3361369963335</v>
       </c>
       <c r="P25">
-        <v>280.8396829349444</v>
+        <v>279.3902963234202</v>
       </c>
       <c r="Q25">
-        <v>327.9396829349444</v>
+        <v>326.4902963234202</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.105989633510276</v>
+        <v>0.1066060502596559</v>
       </c>
       <c r="T25">
-        <v>0.7210563000612823</v>
+        <v>0.7284408138833812</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.424543803624053</v>
+        <v>9.031854478473051</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,22 +3380,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09039379819733849</v>
+        <v>0.09019292859176446</v>
       </c>
       <c r="C26">
-        <v>3091.047793764217</v>
+        <v>3065.798459127792</v>
       </c>
       <c r="D26">
-        <v>3649.821937320221</v>
+        <v>3661.684025331963</v>
       </c>
       <c r="E26">
-        <v>-364.9681212606812</v>
+        <v>-327.8566986125143</v>
       </c>
       <c r="F26">
-        <v>890.6741435560044</v>
+        <v>927.7855662041713</v>
       </c>
       <c r="G26">
         <v>331.9</v>
@@ -3416,28 +3416,28 @@
         <v>430.3775</v>
       </c>
       <c r="M26">
-        <v>47.65106668024624</v>
+        <v>49.63652779192316</v>
       </c>
       <c r="N26">
-        <v>382.7264333197538</v>
+        <v>380.7409722080768</v>
       </c>
       <c r="O26">
-        <v>103.3361369963335</v>
+        <v>102.8000624961807</v>
       </c>
       <c r="P26">
-        <v>279.3902963234202</v>
+        <v>277.9409097118961</v>
       </c>
       <c r="Q26">
-        <v>326.4902963234202</v>
+        <v>325.0409097118961</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1066060502596559</v>
+        <v>0.1072389047890193</v>
       </c>
       <c r="T26">
-        <v>0.7284408138833812</v>
+        <v>0.7360222480740694</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.031854478473052</v>
+        <v>8.67058029933413</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,22 +3462,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09019292859176446</v>
+        <v>0.08999205898619046</v>
       </c>
       <c r="C27">
-        <v>3065.798459127792</v>
+        <v>3040.626480557857</v>
       </c>
       <c r="D27">
-        <v>3661.684025331963</v>
+        <v>3673.623469410195</v>
       </c>
       <c r="E27">
-        <v>-327.8566986125143</v>
+        <v>-290.7452759643473</v>
       </c>
       <c r="F27">
-        <v>927.7855662041713</v>
+        <v>964.8969888523383</v>
       </c>
       <c r="G27">
         <v>331.9</v>
@@ -3498,28 +3498,28 @@
         <v>430.3775</v>
       </c>
       <c r="M27">
-        <v>49.63652779192316</v>
+        <v>51.6219889036001</v>
       </c>
       <c r="N27">
-        <v>380.7409722080768</v>
+        <v>378.7555110963999</v>
       </c>
       <c r="O27">
-        <v>102.8000624961807</v>
+        <v>102.263987996028</v>
       </c>
       <c r="P27">
-        <v>277.9409097118961</v>
+        <v>276.4915231003719</v>
       </c>
       <c r="Q27">
-        <v>325.0409097118961</v>
+        <v>323.5915231003719</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1072389047890193</v>
+        <v>0.107888863494852</v>
       </c>
       <c r="T27">
-        <v>0.7360222480740694</v>
+        <v>0.7438085858915329</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.67058029933413</v>
+        <v>8.33709644166743</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,22 +3544,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08999205898619046</v>
+        <v>0.08979118938061643</v>
       </c>
       <c r="C28">
-        <v>3040.626480557857</v>
+        <v>3015.532617221318</v>
       </c>
       <c r="D28">
-        <v>3673.623469410195</v>
+        <v>3685.641028721823</v>
       </c>
       <c r="E28">
-        <v>-290.7452759643473</v>
+        <v>-253.6338533161805</v>
       </c>
       <c r="F28">
-        <v>964.8969888523383</v>
+        <v>1002.008411500505</v>
       </c>
       <c r="G28">
         <v>331.9</v>
@@ -3580,28 +3580,28 @@
         <v>430.3775</v>
       </c>
       <c r="M28">
-        <v>51.6219889036001</v>
+        <v>53.60745001527702</v>
       </c>
       <c r="N28">
-        <v>378.7555110963999</v>
+        <v>376.770049984723</v>
       </c>
       <c r="O28">
-        <v>102.263987996028</v>
+        <v>101.7279134958752</v>
       </c>
       <c r="P28">
-        <v>276.4915231003719</v>
+        <v>275.0421364888477</v>
       </c>
       <c r="Q28">
-        <v>323.5915231003719</v>
+        <v>322.1421364888477</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.107888863494852</v>
+        <v>0.1085566292885157</v>
       </c>
       <c r="T28">
-        <v>0.7438085858915329</v>
+        <v>0.7518082480327625</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.33709644166743</v>
+        <v>8.028315091976046</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,22 +3626,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08979118938061643</v>
+        <v>0.08959031977504243</v>
       </c>
       <c r="C29">
-        <v>3015.532617221318</v>
+        <v>2990.517638251558</v>
       </c>
       <c r="D29">
-        <v>3685.641028721823</v>
+        <v>3697.73747240023</v>
       </c>
       <c r="E29">
-        <v>-253.6338533161805</v>
+        <v>-216.5224306680136</v>
       </c>
       <c r="F29">
-        <v>1002.008411500505</v>
+        <v>1039.119834148672</v>
       </c>
       <c r="G29">
         <v>331.9</v>
@@ -3662,28 +3662,28 @@
         <v>430.3775</v>
       </c>
       <c r="M29">
-        <v>53.60745001527702</v>
+        <v>55.59291112695395</v>
       </c>
       <c r="N29">
-        <v>376.770049984723</v>
+        <v>374.7845888730461</v>
       </c>
       <c r="O29">
-        <v>101.7279134958752</v>
+        <v>101.1918389957224</v>
       </c>
       <c r="P29">
-        <v>275.0421364888477</v>
+        <v>273.5927498773236</v>
       </c>
       <c r="Q29">
-        <v>322.1421364888477</v>
+        <v>320.6927498773236</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1085566292885157</v>
+        <v>0.1092429441320034</v>
       </c>
       <c r="T29">
-        <v>0.7518082480327625</v>
+        <v>0.7600301230112485</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.028315091976046</v>
+        <v>7.741589552976901</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,22 +3708,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08959031977504243</v>
+        <v>0.08955881016946843</v>
       </c>
       <c r="C30">
-        <v>2990.517638251558</v>
+        <v>2955.310944360103</v>
       </c>
       <c r="D30">
-        <v>3697.73747240023</v>
+        <v>3699.642201156942</v>
       </c>
       <c r="E30">
-        <v>-216.5224306680136</v>
+        <v>-179.4110080198468</v>
       </c>
       <c r="F30">
-        <v>1039.119834148672</v>
+        <v>1076.231256796839</v>
       </c>
       <c r="G30">
         <v>331.9</v>
@@ -3744,45 +3744,45 @@
         <v>430.3775</v>
       </c>
       <c r="M30">
-        <v>55.59291112695395</v>
+        <v>58.43935724406835</v>
       </c>
       <c r="N30">
-        <v>374.7845888730461</v>
+        <v>371.9381427559317</v>
       </c>
       <c r="O30">
-        <v>101.1918389957224</v>
+        <v>100.4232985441016</v>
       </c>
       <c r="P30">
-        <v>273.5927498773236</v>
+        <v>271.5148442118301</v>
       </c>
       <c r="Q30">
-        <v>320.6927498773236</v>
+        <v>318.6148442118301</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1092429441320034</v>
+        <v>0.1099485917879837</v>
       </c>
       <c r="T30">
-        <v>0.7600301230112485</v>
+        <v>0.7684836001018046</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.741589552976901</v>
+        <v>7.364514606184922</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,22 +3790,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08955881016946843</v>
+        <v>0.08936378056389442</v>
       </c>
       <c r="C31">
-        <v>2955.310944360103</v>
+        <v>2930.032694964265</v>
       </c>
       <c r="D31">
-        <v>3699.642201156942</v>
+        <v>3711.47537440927</v>
       </c>
       <c r="E31">
-        <v>-179.411008019847</v>
+        <v>-142.29958537168</v>
       </c>
       <c r="F31">
-        <v>1076.231256796839</v>
+        <v>1113.342679445006</v>
       </c>
       <c r="G31">
         <v>331.9</v>
@@ -3826,28 +3826,28 @@
         <v>430.3775</v>
       </c>
       <c r="M31">
-        <v>58.43935724406833</v>
+        <v>60.45450749386381</v>
       </c>
       <c r="N31">
-        <v>371.9381427559317</v>
+        <v>369.9229925061362</v>
       </c>
       <c r="O31">
-        <v>100.4232985441016</v>
+        <v>99.87920797665679</v>
       </c>
       <c r="P31">
-        <v>271.5148442118301</v>
+        <v>270.0437845294794</v>
       </c>
       <c r="Q31">
-        <v>318.6148442118301</v>
+        <v>317.1437845294794</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1099485917879837</v>
+        <v>0.1106744008055635</v>
       </c>
       <c r="T31">
-        <v>0.7684836001018046</v>
+        <v>0.7771786051092338</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.364514606184924</v>
+        <v>7.119030785978759</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,22 +3872,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08936378056389442</v>
+        <v>0.08916875095832041</v>
       </c>
       <c r="C32">
-        <v>2930.032694964265</v>
+        <v>2904.830384418925</v>
       </c>
       <c r="D32">
-        <v>3711.47537440927</v>
+        <v>3723.384486512098</v>
       </c>
       <c r="E32">
-        <v>-142.29958537168</v>
+        <v>-105.1881627235132</v>
       </c>
       <c r="F32">
-        <v>1113.342679445006</v>
+        <v>1150.454102093172</v>
       </c>
       <c r="G32">
         <v>331.9</v>
@@ -3908,28 +3908,28 @@
         <v>430.3775</v>
       </c>
       <c r="M32">
-        <v>60.45450749386381</v>
+        <v>62.46965774365926</v>
       </c>
       <c r="N32">
-        <v>369.9229925061362</v>
+        <v>367.9078422563408</v>
       </c>
       <c r="O32">
-        <v>99.87920797665679</v>
+        <v>99.33511740921202</v>
       </c>
       <c r="P32">
-        <v>270.0437845294794</v>
+        <v>268.5727248471287</v>
       </c>
       <c r="Q32">
-        <v>317.1437845294794</v>
+        <v>315.6727248471287</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1106744008055635</v>
+        <v>0.1114212477656818</v>
       </c>
       <c r="T32">
-        <v>0.7771786051092338</v>
+        <v>0.7861256392473129</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.119030785978759</v>
+        <v>6.889384631592348</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,22 +3954,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08916875095832041</v>
+        <v>0.08897372135274641</v>
       </c>
       <c r="C33">
-        <v>2904.830384418925</v>
+        <v>2879.704746078392</v>
       </c>
       <c r="D33">
-        <v>3723.384486512098</v>
+        <v>3735.370270819732</v>
       </c>
       <c r="E33">
-        <v>-105.1881627235132</v>
+        <v>-68.07674007534615</v>
       </c>
       <c r="F33">
-        <v>1150.454102093172</v>
+        <v>1187.565524741339</v>
       </c>
       <c r="G33">
         <v>331.9</v>
@@ -3990,28 +3990,28 @@
         <v>430.3775</v>
       </c>
       <c r="M33">
-        <v>62.46965774365926</v>
+        <v>64.48480799345474</v>
       </c>
       <c r="N33">
-        <v>367.9078422563408</v>
+        <v>365.8926920065452</v>
       </c>
       <c r="O33">
-        <v>99.33511740921202</v>
+        <v>98.79102684176722</v>
       </c>
       <c r="P33">
-        <v>268.5727248471287</v>
+        <v>267.101665164778</v>
       </c>
       <c r="Q33">
-        <v>315.6727248471287</v>
+        <v>314.201665164778</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1114212477656818</v>
+        <v>0.1121900608128624</v>
       </c>
       <c r="T33">
-        <v>0.7861256392473129</v>
+        <v>0.7953358214482767</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.889384631592348</v>
+        <v>6.674091361855084</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,22 +4036,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08897372135274641</v>
+        <v>0.08877869174717237</v>
       </c>
       <c r="C34">
-        <v>2879.704746078392</v>
+        <v>2854.656522770303</v>
       </c>
       <c r="D34">
-        <v>3735.370270819732</v>
+        <v>3747.433470159809</v>
       </c>
       <c r="E34">
-        <v>-68.07674007534615</v>
+        <v>-30.96531742717934</v>
       </c>
       <c r="F34">
-        <v>1187.565524741339</v>
+        <v>1224.676947389506</v>
       </c>
       <c r="G34">
         <v>331.9</v>
@@ -4072,28 +4072,28 @@
         <v>430.3775</v>
       </c>
       <c r="M34">
-        <v>64.48480799345474</v>
+        <v>66.49995824325019</v>
       </c>
       <c r="N34">
-        <v>365.8926920065452</v>
+        <v>363.8775417567498</v>
       </c>
       <c r="O34">
-        <v>98.79102684176722</v>
+        <v>98.24693627432245</v>
       </c>
       <c r="P34">
-        <v>267.101665164778</v>
+        <v>265.6306054824273</v>
       </c>
       <c r="Q34">
-        <v>314.201665164778</v>
+        <v>312.7306054824273</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1121900608128624</v>
+        <v>0.1129818235032424</v>
       </c>
       <c r="T34">
-        <v>0.7953358214482767</v>
+        <v>0.8048209344612097</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.674091361855084</v>
+        <v>6.471846169071598</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,22 +4118,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08877869174717237</v>
+        <v>0.08858366214159838</v>
       </c>
       <c r="C35">
-        <v>2854.656522770303</v>
+        <v>2829.686466949084</v>
       </c>
       <c r="D35">
-        <v>3747.433470159809</v>
+        <v>3759.574836986757</v>
       </c>
       <c r="E35">
-        <v>-30.96531742717934</v>
+        <v>6.146105220987465</v>
       </c>
       <c r="F35">
-        <v>1224.676947389506</v>
+        <v>1261.788370037673</v>
       </c>
       <c r="G35">
         <v>331.9</v>
@@ -4154,28 +4154,28 @@
         <v>430.3775</v>
       </c>
       <c r="M35">
-        <v>66.49995824325019</v>
+        <v>68.51510849304564</v>
       </c>
       <c r="N35">
-        <v>363.8775417567498</v>
+        <v>361.8623915069543</v>
       </c>
       <c r="O35">
-        <v>98.24693627432245</v>
+        <v>97.70284570687768</v>
       </c>
       <c r="P35">
-        <v>265.6306054824273</v>
+        <v>264.1595458000767</v>
       </c>
       <c r="Q35">
-        <v>312.7306054824273</v>
+        <v>311.2595458000766</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1129818235032424</v>
+        <v>0.1137975790024218</v>
       </c>
       <c r="T35">
-        <v>0.8048209344612097</v>
+        <v>0.8145934751412013</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.471846169071598</v>
+        <v>6.281497752334198</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,22 +4200,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08858366214159838</v>
+        <v>0.08864413253602436</v>
       </c>
       <c r="C36">
-        <v>2829.686466949084</v>
+        <v>2788.802115701775</v>
       </c>
       <c r="D36">
-        <v>3759.574836986757</v>
+        <v>3755.801908387615</v>
       </c>
       <c r="E36">
-        <v>6.146105220987465</v>
+        <v>43.2575278691545</v>
       </c>
       <c r="F36">
-        <v>1261.788370037673</v>
+        <v>1298.89979268584</v>
       </c>
       <c r="G36">
         <v>331.9</v>
@@ -4236,45 +4236,45 @@
         <v>430.3775</v>
       </c>
       <c r="M36">
-        <v>68.51510849304564</v>
+        <v>71.82915853552696</v>
       </c>
       <c r="N36">
-        <v>361.8623915069543</v>
+        <v>358.548341464473</v>
       </c>
       <c r="O36">
-        <v>97.70284570687768</v>
+        <v>96.80805219540773</v>
       </c>
       <c r="P36">
-        <v>264.1595458000767</v>
+        <v>261.7402892690653</v>
       </c>
       <c r="Q36">
-        <v>311.2595458000766</v>
+        <v>308.8402892690653</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1137975790024218</v>
+        <v>0.1146384346708067</v>
       </c>
       <c r="T36">
-        <v>0.8145934751412013</v>
+        <v>0.8246667093805772</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.27</v>
       </c>
       <c r="W36">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.281497752334198</v>
+        <v>5.991682330332935</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,22 +4282,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08864413253602436</v>
+        <v>0.08845640293045036</v>
       </c>
       <c r="C37">
-        <v>2788.802115701775</v>
+        <v>2763.428518853199</v>
       </c>
       <c r="D37">
-        <v>3755.801908387615</v>
+        <v>3767.539734187206</v>
       </c>
       <c r="E37">
-        <v>43.2575278691545</v>
+        <v>80.36895051732131</v>
       </c>
       <c r="F37">
-        <v>1298.89979268584</v>
+        <v>1336.011215334007</v>
       </c>
       <c r="G37">
         <v>331.9</v>
@@ -4318,28 +4318,28 @@
         <v>430.3775</v>
       </c>
       <c r="M37">
-        <v>71.82915853552696</v>
+        <v>73.88142020797059</v>
       </c>
       <c r="N37">
-        <v>358.548341464473</v>
+        <v>356.4960797920294</v>
       </c>
       <c r="O37">
-        <v>96.80805219540773</v>
+        <v>96.25394154384794</v>
       </c>
       <c r="P37">
-        <v>261.7402892690653</v>
+        <v>260.2421382481814</v>
       </c>
       <c r="Q37">
-        <v>308.8402892690653</v>
+        <v>307.3421382481814</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1146384346708067</v>
+        <v>0.1155055670788287</v>
       </c>
       <c r="T37">
-        <v>0.8246667093805772</v>
+        <v>0.8350547321899335</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.991682330332935</v>
+        <v>5.825246710045908</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,22 +4364,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08845640293045037</v>
+        <v>0.08826867332487635</v>
       </c>
       <c r="C38">
-        <v>2763.428518853198</v>
+        <v>2738.128519331733</v>
       </c>
       <c r="D38">
-        <v>3767.539734187205</v>
+        <v>3779.351157313906</v>
       </c>
       <c r="E38">
-        <v>80.36895051732108</v>
+        <v>117.4803731654879</v>
       </c>
       <c r="F38">
-        <v>1336.011215334007</v>
+        <v>1373.122637982174</v>
       </c>
       <c r="G38">
         <v>331.9</v>
@@ -4400,28 +4400,28 @@
         <v>430.3775</v>
       </c>
       <c r="M38">
-        <v>73.88142020797058</v>
+        <v>75.9336818804142</v>
       </c>
       <c r="N38">
-        <v>356.4960797920294</v>
+        <v>354.4438181195858</v>
       </c>
       <c r="O38">
-        <v>96.25394154384796</v>
+        <v>95.69983089228816</v>
       </c>
       <c r="P38">
-        <v>260.2421382481815</v>
+        <v>258.7439872272976</v>
       </c>
       <c r="Q38">
-        <v>307.3421382481815</v>
+        <v>305.8439872272976</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1155055670788287</v>
+        <v>0.1164002274998037</v>
       </c>
       <c r="T38">
-        <v>0.8350547321899335</v>
+        <v>0.8457725335011742</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.82524671004591</v>
+        <v>5.667807609774399</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,22 +4446,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08826867332487635</v>
+        <v>0.08808094371930235</v>
       </c>
       <c r="C39">
-        <v>2738.128519331733</v>
+        <v>2712.902811508026</v>
       </c>
       <c r="D39">
-        <v>3779.351157313906</v>
+        <v>3791.236872138367</v>
       </c>
       <c r="E39">
-        <v>117.4803731654879</v>
+        <v>154.5917958136549</v>
       </c>
       <c r="F39">
-        <v>1373.122637982174</v>
+        <v>1410.234060630341</v>
       </c>
       <c r="G39">
         <v>331.9</v>
@@ -4482,28 +4482,28 @@
         <v>430.3775</v>
       </c>
       <c r="M39">
-        <v>75.9336818804142</v>
+        <v>77.98594355285783</v>
       </c>
       <c r="N39">
-        <v>354.4438181195858</v>
+        <v>352.3915564471422</v>
       </c>
       <c r="O39">
-        <v>95.69983089228816</v>
+        <v>95.14572024072839</v>
       </c>
       <c r="P39">
-        <v>258.7439872272976</v>
+        <v>257.2458362064138</v>
       </c>
       <c r="Q39">
-        <v>305.8439872272976</v>
+        <v>304.3458362064138</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1164002274998037</v>
+        <v>0.1173237479343586</v>
       </c>
       <c r="T39">
-        <v>0.8457725335011742</v>
+        <v>0.856836070338584</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.667807609774399</v>
+        <v>5.518654777938231</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,22 +4528,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08808094371930235</v>
+        <v>0.08789321411372833</v>
       </c>
       <c r="C40">
-        <v>2712.902811508026</v>
+        <v>2687.75209851522</v>
       </c>
       <c r="D40">
-        <v>3791.236872138367</v>
+        <v>3803.197581793727</v>
       </c>
       <c r="E40">
-        <v>154.5917958136549</v>
+        <v>191.7032184618217</v>
       </c>
       <c r="F40">
-        <v>1410.234060630341</v>
+        <v>1447.345483278507</v>
       </c>
       <c r="G40">
         <v>331.9</v>
@@ -4564,28 +4564,28 @@
         <v>430.3775</v>
       </c>
       <c r="M40">
-        <v>77.98594355285783</v>
+        <v>80.03820522530145</v>
       </c>
       <c r="N40">
-        <v>352.3915564471422</v>
+        <v>350.3392947746985</v>
       </c>
       <c r="O40">
-        <v>95.14572024072839</v>
+        <v>94.59160958916861</v>
       </c>
       <c r="P40">
-        <v>257.2458362064138</v>
+        <v>255.7476851855299</v>
       </c>
       <c r="Q40">
-        <v>304.3458362064138</v>
+        <v>302.8476851855299</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1173237479343586</v>
+        <v>0.1182775477274235</v>
       </c>
       <c r="T40">
-        <v>0.856836070338584</v>
+        <v>0.8682623460886958</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4602,7 +4602,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.518654777938231</v>
+        <v>5.377150809273147</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,22 +4610,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08789321411372833</v>
+        <v>0.08770548450815432</v>
       </c>
       <c r="C41">
-        <v>2687.75209851522</v>
+        <v>2662.677092387595</v>
       </c>
       <c r="D41">
-        <v>3803.197581793727</v>
+        <v>3815.233998314269</v>
       </c>
       <c r="E41">
-        <v>191.7032184618217</v>
+        <v>228.8146411099885</v>
       </c>
       <c r="F41">
-        <v>1447.345483278507</v>
+        <v>1484.456905926674</v>
       </c>
       <c r="G41">
         <v>331.9</v>
@@ -4646,28 +4646,28 @@
         <v>430.3775</v>
       </c>
       <c r="M41">
-        <v>80.03820522530145</v>
+        <v>82.09046689774509</v>
       </c>
       <c r="N41">
-        <v>350.3392947746985</v>
+        <v>348.2870331022549</v>
       </c>
       <c r="O41">
-        <v>94.59160958916861</v>
+        <v>94.03749893760883</v>
       </c>
       <c r="P41">
-        <v>255.7476851855299</v>
+        <v>254.2495341646461</v>
       </c>
       <c r="Q41">
-        <v>302.8476851855299</v>
+        <v>301.349534164646</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1182775477274235</v>
+        <v>0.1192631408469239</v>
       </c>
       <c r="T41">
-        <v>0.8682623460886958</v>
+        <v>0.8800694976971446</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.377150809273147</v>
+        <v>5.242722039041318</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,22 +4692,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08770548450815432</v>
+        <v>0.08751775490258032</v>
       </c>
       <c r="C42">
-        <v>2662.677092387595</v>
+        <v>2637.67851420188</v>
       </c>
       <c r="D42">
-        <v>3815.233998314269</v>
+        <v>3827.346842776721</v>
       </c>
       <c r="E42">
-        <v>228.8146411099885</v>
+        <v>265.9260637581556</v>
       </c>
       <c r="F42">
-        <v>1484.456905926674</v>
+        <v>1521.568328574841</v>
       </c>
       <c r="G42">
         <v>331.9</v>
@@ -4728,28 +4728,28 @@
         <v>430.3775</v>
       </c>
       <c r="M42">
-        <v>82.09046689774509</v>
+        <v>84.14272857018872</v>
       </c>
       <c r="N42">
-        <v>348.2870331022549</v>
+        <v>346.2347714298113</v>
       </c>
       <c r="O42">
-        <v>94.03749893760883</v>
+        <v>93.48338828604906</v>
       </c>
       <c r="P42">
-        <v>254.2495341646461</v>
+        <v>252.7513831437622</v>
       </c>
       <c r="Q42">
-        <v>301.349534164646</v>
+        <v>299.8513831437622</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1192631408469239</v>
+        <v>0.1202821439026785</v>
       </c>
       <c r="T42">
-        <v>0.8800694976971446</v>
+        <v>0.8922768917329984</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.242722039041318</v>
+        <v>5.114850769796409</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,22 +4774,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08751775490258032</v>
+        <v>0.08733002529700631</v>
       </c>
       <c r="C43">
-        <v>2637.67851420188</v>
+        <v>2612.757094221248</v>
       </c>
       <c r="D43">
-        <v>3827.346842776721</v>
+        <v>3839.536845444256</v>
       </c>
       <c r="E43">
-        <v>265.9260637581556</v>
+        <v>303.0374864063224</v>
       </c>
       <c r="F43">
-        <v>1521.568328574841</v>
+        <v>1558.679751223008</v>
       </c>
       <c r="G43">
         <v>331.9</v>
@@ -4810,28 +4810,28 @@
         <v>430.3775</v>
       </c>
       <c r="M43">
-        <v>84.14272857018872</v>
+        <v>86.19499024263234</v>
       </c>
       <c r="N43">
-        <v>346.2347714298113</v>
+        <v>344.1825097573677</v>
       </c>
       <c r="O43">
-        <v>93.48338828604906</v>
+        <v>92.92927763448927</v>
       </c>
       <c r="P43">
-        <v>252.7513831437622</v>
+        <v>251.2532321228784</v>
       </c>
       <c r="Q43">
-        <v>299.8513831437622</v>
+        <v>298.3532321228784</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1202821439026785</v>
+        <v>0.1213362849948385</v>
       </c>
       <c r="T43">
-        <v>0.8922768917329984</v>
+        <v>0.9049052303907783</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.114850769796409</v>
+        <v>4.99306860861078</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,22 +4856,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08733002529700631</v>
+        <v>0.08714229569143231</v>
       </c>
       <c r="C44">
-        <v>2612.757094221248</v>
+        <v>2587.913572042075</v>
       </c>
       <c r="D44">
-        <v>3839.536845444256</v>
+        <v>3851.80474591325</v>
       </c>
       <c r="E44">
-        <v>303.0374864063222</v>
+        <v>340.148909054489</v>
       </c>
       <c r="F44">
-        <v>1558.679751223008</v>
+        <v>1595.791173871175</v>
       </c>
       <c r="G44">
         <v>331.9</v>
@@ -4892,28 +4892,28 @@
         <v>430.3775</v>
       </c>
       <c r="M44">
-        <v>86.19499024263233</v>
+        <v>88.24725191507596</v>
       </c>
       <c r="N44">
-        <v>344.1825097573677</v>
+        <v>342.130248084924</v>
       </c>
       <c r="O44">
-        <v>92.92927763448927</v>
+        <v>92.37516698292949</v>
       </c>
       <c r="P44">
-        <v>251.2532321228784</v>
+        <v>249.7550811019945</v>
       </c>
       <c r="Q44">
-        <v>298.3532321228784</v>
+        <v>296.8550811019945</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1213362849948385</v>
+        <v>0.1224274134937409</v>
       </c>
       <c r="T44">
-        <v>0.9049052303907781</v>
+        <v>0.9179766686505855</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4930,7 +4930,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.993068608610781</v>
+        <v>4.876950733991924</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,22 +4938,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08714229569143231</v>
+        <v>0.0869545660858583</v>
       </c>
       <c r="C45">
-        <v>2587.913572042075</v>
+        <v>2563.148696743528</v>
       </c>
       <c r="D45">
-        <v>3851.80474591325</v>
+        <v>3864.15129326287</v>
       </c>
       <c r="E45">
-        <v>340.148909054489</v>
+        <v>377.260331702656</v>
       </c>
       <c r="F45">
-        <v>1595.791173871175</v>
+        <v>1632.902596519342</v>
       </c>
       <c r="G45">
         <v>331.9</v>
@@ -4974,28 +4974,28 @@
         <v>430.3775</v>
       </c>
       <c r="M45">
-        <v>88.24725191507596</v>
+        <v>90.2995135875196</v>
       </c>
       <c r="N45">
-        <v>342.130248084924</v>
+        <v>340.0779864124804</v>
       </c>
       <c r="O45">
-        <v>92.37516698292949</v>
+        <v>91.82105633136972</v>
       </c>
       <c r="P45">
-        <v>249.7550811019945</v>
+        <v>248.2569300811107</v>
       </c>
       <c r="Q45">
-        <v>296.8550811019945</v>
+        <v>295.3569300811106</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1224274134937409</v>
+        <v>0.1235575108676041</v>
       </c>
       <c r="T45">
-        <v>0.9179766686505855</v>
+        <v>0.9315149439910999</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.876950733991924</v>
+        <v>4.766110944583017</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,22 +5020,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0869545660858583</v>
+        <v>0.08676683648028427</v>
       </c>
       <c r="C46">
-        <v>2563.148696743528</v>
+        <v>2538.463227040029</v>
       </c>
       <c r="D46">
-        <v>3864.15129326287</v>
+        <v>3876.577246207537</v>
       </c>
       <c r="E46">
-        <v>377.260331702656</v>
+        <v>414.3717543508228</v>
       </c>
       <c r="F46">
-        <v>1632.902596519342</v>
+        <v>1670.014019167508</v>
       </c>
       <c r="G46">
         <v>331.9</v>
@@ -5056,28 +5056,28 @@
         <v>430.3775</v>
       </c>
       <c r="M46">
-        <v>90.2995135875196</v>
+        <v>92.35177525996322</v>
       </c>
       <c r="N46">
-        <v>340.0779864124804</v>
+        <v>338.0257247400368</v>
       </c>
       <c r="O46">
-        <v>91.82105633136972</v>
+        <v>91.26694567980994</v>
       </c>
       <c r="P46">
-        <v>248.2569300811107</v>
+        <v>246.7587790602268</v>
       </c>
       <c r="Q46">
-        <v>295.3569300811106</v>
+        <v>293.8587790602268</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1235575108676041</v>
+        <v>0.1247287026914259</v>
       </c>
       <c r="T46">
-        <v>0.9315149439910999</v>
+        <v>0.9455455202530878</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.766110944583017</v>
+        <v>4.660197368036728</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,22 +5102,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08676683648028427</v>
+        <v>0.08657910687471027</v>
       </c>
       <c r="C47">
-        <v>2538.463227040029</v>
+        <v>2513.857931436673</v>
       </c>
       <c r="D47">
-        <v>3876.577246207537</v>
+        <v>3889.083373252348</v>
       </c>
       <c r="E47">
-        <v>414.3717543508228</v>
+        <v>451.4831769989898</v>
       </c>
       <c r="F47">
-        <v>1670.014019167508</v>
+        <v>1707.125441815675</v>
       </c>
       <c r="G47">
         <v>331.9</v>
@@ -5138,28 +5138,28 @@
         <v>430.3775</v>
       </c>
       <c r="M47">
-        <v>92.35177525996322</v>
+        <v>94.40403693240685</v>
       </c>
       <c r="N47">
-        <v>338.0257247400368</v>
+        <v>335.9734630675931</v>
       </c>
       <c r="O47">
-        <v>91.26694567980994</v>
+        <v>90.71283502825014</v>
       </c>
       <c r="P47">
-        <v>246.7587790602268</v>
+        <v>245.260628039343</v>
       </c>
       <c r="Q47">
-        <v>293.8587790602268</v>
+        <v>292.3606280393429</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1247287026914259</v>
+        <v>0.1259432719902042</v>
       </c>
       <c r="T47">
-        <v>0.9455455202530878</v>
+        <v>0.960095747487742</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.660197368036728</v>
+        <v>4.558888729601146</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,22 +5184,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08657910687471027</v>
+        <v>0.08724912726913626</v>
       </c>
       <c r="C48">
-        <v>2513.857931436673</v>
+        <v>2432.476973314343</v>
       </c>
       <c r="D48">
-        <v>3889.083373252348</v>
+        <v>3844.813837778185</v>
       </c>
       <c r="E48">
-        <v>451.4831769989898</v>
+        <v>488.5945996471567</v>
       </c>
       <c r="F48">
-        <v>1707.125441815675</v>
+        <v>1744.236864463842</v>
       </c>
       <c r="G48">
         <v>331.9</v>
@@ -5220,45 +5220,45 @@
         <v>430.3775</v>
       </c>
       <c r="M48">
-        <v>94.40403693240685</v>
+        <v>100.8168907660101</v>
       </c>
       <c r="N48">
-        <v>335.9734630675931</v>
+        <v>329.5606092339899</v>
       </c>
       <c r="O48">
-        <v>90.71283502825014</v>
+        <v>88.98136449317728</v>
       </c>
       <c r="P48">
-        <v>245.260628039343</v>
+        <v>240.5792447408126</v>
       </c>
       <c r="Q48">
-        <v>292.3606280393429</v>
+        <v>287.6792447408126</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1259432719902042</v>
+        <v>0.1272036740927099</v>
       </c>
       <c r="T48">
-        <v>0.960095747487742</v>
+        <v>0.9751950399010622</v>
       </c>
       <c r="U48">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V48">
         <v>0.27</v>
       </c>
       <c r="W48">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.558888729601146</v>
+        <v>4.268902727806595</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,22 +5266,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08724912726913626</v>
+        <v>0.08707964766356224</v>
       </c>
       <c r="C49">
-        <v>2432.476973314343</v>
+        <v>2406.467895666613</v>
       </c>
       <c r="D49">
-        <v>3844.813837778185</v>
+        <v>3855.916182778622</v>
       </c>
       <c r="E49">
-        <v>488.5945996471567</v>
+        <v>525.7060222953235</v>
       </c>
       <c r="F49">
-        <v>1744.236864463842</v>
+        <v>1781.348287112009</v>
       </c>
       <c r="G49">
         <v>331.9</v>
@@ -5302,28 +5302,28 @@
         <v>430.3775</v>
       </c>
       <c r="M49">
-        <v>100.8168907660101</v>
+        <v>102.9619309950741</v>
       </c>
       <c r="N49">
-        <v>329.5606092339899</v>
+        <v>327.4155690049259</v>
       </c>
       <c r="O49">
-        <v>88.98136449317728</v>
+        <v>88.40220363133</v>
       </c>
       <c r="P49">
-        <v>240.5792447408126</v>
+        <v>239.0133653735959</v>
       </c>
       <c r="Q49">
-        <v>287.6792447408126</v>
+        <v>286.1133653735959</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1272036740927099</v>
+        <v>0.1285125531991582</v>
       </c>
       <c r="T49">
-        <v>0.9751950399010622</v>
+        <v>0.9908750743302793</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5340,7 +5340,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.268902727806595</v>
+        <v>4.179967254310625</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,22 +5348,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08707964766356224</v>
+        <v>0.08691016805798824</v>
       </c>
       <c r="C50">
-        <v>2406.467895666613</v>
+        <v>2380.523122317596</v>
       </c>
       <c r="D50">
-        <v>3855.916182778622</v>
+        <v>3867.082832077772</v>
       </c>
       <c r="E50">
-        <v>525.7060222953232</v>
+        <v>562.8174449434903</v>
       </c>
       <c r="F50">
-        <v>1781.348287112009</v>
+        <v>1818.459709760176</v>
       </c>
       <c r="G50">
         <v>331.9</v>
@@ -5384,28 +5384,28 @@
         <v>430.3775</v>
       </c>
       <c r="M50">
-        <v>102.9619309950741</v>
+        <v>105.1069712241382</v>
       </c>
       <c r="N50">
-        <v>327.4155690049259</v>
+        <v>325.2705287758618</v>
       </c>
       <c r="O50">
-        <v>88.40220363133</v>
+        <v>87.8230427694827</v>
       </c>
       <c r="P50">
-        <v>239.0133653735959</v>
+        <v>237.4474860063791</v>
       </c>
       <c r="Q50">
-        <v>286.1133653735959</v>
+        <v>284.5474860063791</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1285125531991582</v>
+        <v>0.1298727608980161</v>
       </c>
       <c r="T50">
-        <v>0.9908750743302793</v>
+        <v>1.007170012070446</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.179967254310625</v>
+        <v>4.09466180014102</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,22 +5430,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08691016805798824</v>
+        <v>0.08674068845241423</v>
       </c>
       <c r="C51">
-        <v>2380.523122317596</v>
+        <v>2354.64321356144</v>
       </c>
       <c r="D51">
-        <v>3867.082832077772</v>
+        <v>3878.314345969783</v>
       </c>
       <c r="E51">
-        <v>562.8174449434903</v>
+        <v>599.9288675916571</v>
       </c>
       <c r="F51">
-        <v>1818.459709760176</v>
+        <v>1855.571132408343</v>
       </c>
       <c r="G51">
         <v>331.9</v>
@@ -5466,28 +5466,28 @@
         <v>430.3775</v>
       </c>
       <c r="M51">
-        <v>105.1069712241382</v>
+        <v>107.2520114532022</v>
       </c>
       <c r="N51">
-        <v>325.2705287758618</v>
+        <v>323.1254885467978</v>
       </c>
       <c r="O51">
-        <v>87.8230427694827</v>
+        <v>87.24388190763541</v>
       </c>
       <c r="P51">
-        <v>237.4474860063791</v>
+        <v>235.8816066391624</v>
       </c>
       <c r="Q51">
-        <v>284.5474860063791</v>
+        <v>282.9816066391624</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1298727608980161</v>
+        <v>0.1312873769048284</v>
       </c>
       <c r="T51">
-        <v>1.007170012070446</v>
+        <v>1.02411674732022</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.09466180014102</v>
+        <v>4.0127685641382</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,22 +5512,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08674068845241423</v>
+        <v>0.08787425884684022</v>
       </c>
       <c r="C52">
-        <v>2354.64321356144</v>
+        <v>2243.626908968579</v>
       </c>
       <c r="D52">
-        <v>3878.314345969783</v>
+        <v>3804.409464025089</v>
       </c>
       <c r="E52">
-        <v>599.9288675916571</v>
+        <v>637.0402902398239</v>
       </c>
       <c r="F52">
-        <v>1855.571132408343</v>
+        <v>1892.682555056509</v>
       </c>
       <c r="G52">
         <v>331.9</v>
@@ -5548,45 +5548,45 @@
         <v>430.3775</v>
       </c>
       <c r="M52">
-        <v>107.2520114532022</v>
+        <v>116.021440624964</v>
       </c>
       <c r="N52">
-        <v>323.1254885467978</v>
+        <v>314.356059375036</v>
       </c>
       <c r="O52">
-        <v>87.24388190763541</v>
+        <v>84.87613603125972</v>
       </c>
       <c r="P52">
-        <v>235.8816066391624</v>
+        <v>229.4799233437762</v>
       </c>
       <c r="Q52">
-        <v>282.9816066391624</v>
+        <v>276.5799233437762</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1312873769048284</v>
+        <v>0.1327597323404902</v>
       </c>
       <c r="T52">
-        <v>1.02411674732022</v>
+        <v>1.041755186049576</v>
       </c>
       <c r="U52">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V52">
         <v>0.27</v>
       </c>
       <c r="W52">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.0127685641382</v>
+        <v>3.709465230579086</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,22 +5594,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08787425884684022</v>
+        <v>0.0877303292412662</v>
       </c>
       <c r="C53">
-        <v>2243.626908968579</v>
+        <v>2215.742710630248</v>
       </c>
       <c r="D53">
-        <v>3804.409464025089</v>
+        <v>3813.636688334925</v>
       </c>
       <c r="E53">
-        <v>637.0402902398239</v>
+        <v>674.1517128879909</v>
       </c>
       <c r="F53">
-        <v>1892.682555056509</v>
+        <v>1929.793977704677</v>
       </c>
       <c r="G53">
         <v>331.9</v>
@@ -5630,28 +5630,28 @@
         <v>430.3775</v>
       </c>
       <c r="M53">
-        <v>116.021440624964</v>
+        <v>118.2963708332967</v>
       </c>
       <c r="N53">
-        <v>314.356059375036</v>
+        <v>312.0811291667033</v>
       </c>
       <c r="O53">
-        <v>84.87613603125972</v>
+        <v>84.2619048750099</v>
       </c>
       <c r="P53">
-        <v>229.4799233437762</v>
+        <v>227.8192242916934</v>
       </c>
       <c r="Q53">
-        <v>276.5799233437762</v>
+        <v>274.9192242916934</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1327597323404902</v>
+        <v>0.1342934359193046</v>
       </c>
       <c r="T53">
-        <v>1.041755186049576</v>
+        <v>1.060128559725989</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.709465230579086</v>
+        <v>3.638129360760257</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,22 +5676,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0877303292412662</v>
+        <v>0.08758639963569219</v>
       </c>
       <c r="C54">
-        <v>2215.742710630248</v>
+        <v>2187.903380581809</v>
       </c>
       <c r="D54">
-        <v>3813.636688334925</v>
+        <v>3822.908780934653</v>
       </c>
       <c r="E54">
-        <v>674.1517128879909</v>
+        <v>711.2631355361577</v>
       </c>
       <c r="F54">
-        <v>1929.793977704677</v>
+        <v>1966.905400352843</v>
       </c>
       <c r="G54">
         <v>331.9</v>
@@ -5712,28 +5712,28 @@
         <v>430.3775</v>
       </c>
       <c r="M54">
-        <v>118.2963708332967</v>
+        <v>120.5713010416293</v>
       </c>
       <c r="N54">
-        <v>312.0811291667033</v>
+        <v>309.8061989583707</v>
       </c>
       <c r="O54">
-        <v>84.2619048750099</v>
+        <v>83.6476737187601</v>
       </c>
       <c r="P54">
-        <v>227.8192242916934</v>
+        <v>226.1585252396106</v>
       </c>
       <c r="Q54">
-        <v>274.9192242916934</v>
+        <v>273.2585252396105</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1342934359193046</v>
+        <v>0.1358924034801962</v>
       </c>
       <c r="T54">
-        <v>1.060128559725989</v>
+        <v>1.079283779090759</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.638129360760257</v>
+        <v>3.569485410557234</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,22 +5758,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08758639963569219</v>
+        <v>0.08744247003011818</v>
       </c>
       <c r="C55">
-        <v>2187.903380581809</v>
+        <v>2160.10924688562</v>
       </c>
       <c r="D55">
-        <v>3822.908780934653</v>
+        <v>3832.226069886631</v>
       </c>
       <c r="E55">
-        <v>711.2631355361577</v>
+        <v>748.3745581843245</v>
       </c>
       <c r="F55">
-        <v>1966.905400352843</v>
+        <v>2004.01682300101</v>
       </c>
       <c r="G55">
         <v>331.9</v>
@@ -5794,28 +5794,28 @@
         <v>430.3775</v>
       </c>
       <c r="M55">
-        <v>120.5713010416293</v>
+        <v>122.8462312499619</v>
       </c>
       <c r="N55">
-        <v>309.8061989583707</v>
+        <v>307.5312687500381</v>
       </c>
       <c r="O55">
-        <v>83.6476737187601</v>
+        <v>83.03344256251029</v>
       </c>
       <c r="P55">
-        <v>226.1585252396106</v>
+        <v>224.4978261875278</v>
       </c>
       <c r="Q55">
-        <v>273.2585252396105</v>
+        <v>271.5978261875277</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1358924034801962</v>
+        <v>0.1375608913698221</v>
       </c>
       <c r="T55">
-        <v>1.079283779090759</v>
+        <v>1.099271834080085</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.569485410557234</v>
+        <v>3.503383828880248</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,22 +5840,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08744247003011818</v>
+        <v>0.08842274042454418</v>
       </c>
       <c r="C56">
-        <v>2160.10924688562</v>
+        <v>2060.424004236549</v>
       </c>
       <c r="D56">
-        <v>3832.226069886631</v>
+        <v>3769.652249885727</v>
       </c>
       <c r="E56">
-        <v>748.3745581843245</v>
+        <v>785.4859808324916</v>
       </c>
       <c r="F56">
-        <v>2004.01682300101</v>
+        <v>2041.128245649177</v>
       </c>
       <c r="G56">
         <v>331.9</v>
@@ -5876,45 +5876,45 @@
         <v>430.3775</v>
       </c>
       <c r="M56">
-        <v>122.8462312499619</v>
+        <v>130.8363205461123</v>
       </c>
       <c r="N56">
-        <v>307.5312687500381</v>
+        <v>299.5411794538877</v>
       </c>
       <c r="O56">
-        <v>83.03344256251029</v>
+        <v>80.87611845254969</v>
       </c>
       <c r="P56">
-        <v>224.4978261875278</v>
+        <v>218.665061001338</v>
       </c>
       <c r="Q56">
-        <v>271.5978261875277</v>
+        <v>265.765061001338</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1375608913698221</v>
+        <v>0.1393035342767649</v>
       </c>
       <c r="T56">
-        <v>1.099271834080085</v>
+        <v>1.120148247068937</v>
       </c>
       <c r="U56">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V56">
         <v>0.27</v>
       </c>
       <c r="W56">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.503383828880248</v>
+        <v>3.289434449116266</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,22 +5922,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08842274042454418</v>
+        <v>0.08829925081897018</v>
       </c>
       <c r="C57">
-        <v>2060.424004236549</v>
+        <v>2031.082591983772</v>
       </c>
       <c r="D57">
-        <v>3769.652249885727</v>
+        <v>3777.422260281116</v>
       </c>
       <c r="E57">
-        <v>785.4859808324916</v>
+        <v>822.5974034806584</v>
       </c>
       <c r="F57">
-        <v>2041.128245649177</v>
+        <v>2078.239668297344</v>
       </c>
       <c r="G57">
         <v>331.9</v>
@@ -5958,28 +5958,28 @@
         <v>430.3775</v>
       </c>
       <c r="M57">
-        <v>130.8363205461123</v>
+        <v>133.2151627378598</v>
       </c>
       <c r="N57">
-        <v>299.5411794538877</v>
+        <v>297.1623372621402</v>
       </c>
       <c r="O57">
-        <v>80.87611845254969</v>
+        <v>80.23383106077786</v>
       </c>
       <c r="P57">
-        <v>218.665061001338</v>
+        <v>216.9285062013624</v>
       </c>
       <c r="Q57">
-        <v>265.765061001338</v>
+        <v>264.0285062013623</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1393035342767649</v>
+        <v>0.1411253882249322</v>
       </c>
       <c r="T57">
-        <v>1.120148247068937</v>
+        <v>1.141973587920918</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5996,7 +5996,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.289434449116266</v>
+        <v>3.23069454823919</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,22 +6004,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08829925081897018</v>
+        <v>0.08817576121339617</v>
       </c>
       <c r="C58">
-        <v>2031.082591983772</v>
+        <v>2001.773276993854</v>
       </c>
       <c r="D58">
-        <v>3777.422260281116</v>
+        <v>3785.224367939365</v>
       </c>
       <c r="E58">
-        <v>822.5974034806584</v>
+        <v>859.7088261288252</v>
       </c>
       <c r="F58">
-        <v>2078.239668297344</v>
+        <v>2115.351090945511</v>
       </c>
       <c r="G58">
         <v>331.9</v>
@@ -6040,28 +6040,28 @@
         <v>430.3775</v>
       </c>
       <c r="M58">
-        <v>133.2151627378598</v>
+        <v>135.5940049296073</v>
       </c>
       <c r="N58">
-        <v>297.1623372621402</v>
+        <v>294.7834950703927</v>
       </c>
       <c r="O58">
-        <v>80.23383106077786</v>
+        <v>79.59154366900604</v>
       </c>
       <c r="P58">
-        <v>216.9285062013624</v>
+        <v>215.1919514013867</v>
       </c>
       <c r="Q58">
-        <v>264.0285062013623</v>
+        <v>262.2919514013867</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1411253882249322</v>
+        <v>0.1430319795660376</v>
       </c>
       <c r="T58">
-        <v>1.141973587920918</v>
+        <v>1.164814060905549</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.23069454823919</v>
+        <v>3.174015696515696</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,22 +6086,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08817576121339617</v>
+        <v>0.08805227160782217</v>
       </c>
       <c r="C59">
-        <v>2001.773276993854</v>
+        <v>1972.496258565099</v>
       </c>
       <c r="D59">
-        <v>3785.224367939365</v>
+        <v>3793.058772158777</v>
       </c>
       <c r="E59">
-        <v>859.7088261288252</v>
+        <v>896.820248776992</v>
       </c>
       <c r="F59">
-        <v>2115.351090945511</v>
+        <v>2152.462513593678</v>
       </c>
       <c r="G59">
         <v>331.9</v>
@@ -6122,28 +6122,28 @@
         <v>430.3775</v>
       </c>
       <c r="M59">
-        <v>135.5940049296073</v>
+        <v>137.9728471213547</v>
       </c>
       <c r="N59">
-        <v>294.7834950703927</v>
+        <v>292.4046528786453</v>
       </c>
       <c r="O59">
-        <v>79.59154366900604</v>
+        <v>78.94925627723423</v>
       </c>
       <c r="P59">
-        <v>215.1919514013867</v>
+        <v>213.4553966014111</v>
       </c>
       <c r="Q59">
-        <v>262.2919514013867</v>
+        <v>260.555396601411</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1430319795660376</v>
+        <v>0.1450293609710052</v>
       </c>
       <c r="T59">
-        <v>1.164814060905549</v>
+        <v>1.188742175460878</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.174015696515696</v>
+        <v>3.11929128795508</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,22 +6168,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08805227160782214</v>
+        <v>0.08792878200224814</v>
       </c>
       <c r="C60">
-        <v>1972.496258565101</v>
+        <v>1943.251737649212</v>
       </c>
       <c r="D60">
-        <v>3793.058772158779</v>
+        <v>3800.925673891057</v>
       </c>
       <c r="E60">
-        <v>896.8202487769915</v>
+        <v>933.9316714251588</v>
       </c>
       <c r="F60">
-        <v>2152.462513593677</v>
+        <v>2189.573936241844</v>
       </c>
       <c r="G60">
         <v>331.9</v>
@@ -6204,28 +6204,28 @@
         <v>430.3775</v>
       </c>
       <c r="M60">
-        <v>137.9728471213547</v>
+        <v>140.3516893131022</v>
       </c>
       <c r="N60">
-        <v>292.4046528786453</v>
+        <v>290.0258106868978</v>
       </c>
       <c r="O60">
-        <v>78.94925627723423</v>
+        <v>78.30696888546241</v>
       </c>
       <c r="P60">
-        <v>213.4553966014111</v>
+        <v>211.7188418014354</v>
       </c>
       <c r="Q60">
-        <v>260.555396601411</v>
+        <v>258.8188418014353</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1450293609710051</v>
+        <v>0.1471241756152394</v>
       </c>
       <c r="T60">
-        <v>1.188742175460877</v>
+        <v>1.213837515116465</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.119291287955081</v>
+        <v>3.066421944091435</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,22 +6250,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08792878200224814</v>
+        <v>0.08780529239667413</v>
       </c>
       <c r="C61">
-        <v>1943.251737649212</v>
+        <v>1914.039916868474</v>
       </c>
       <c r="D61">
-        <v>3800.925673891057</v>
+        <v>3808.825275758486</v>
       </c>
       <c r="E61">
-        <v>933.9316714251588</v>
+        <v>971.0430940733256</v>
       </c>
       <c r="F61">
-        <v>2189.573936241844</v>
+        <v>2226.685358890011</v>
       </c>
       <c r="G61">
         <v>331.9</v>
@@ -6286,28 +6286,28 @@
         <v>430.3775</v>
       </c>
       <c r="M61">
-        <v>140.3516893131022</v>
+        <v>142.7305315048497</v>
       </c>
       <c r="N61">
-        <v>290.0258106868978</v>
+        <v>287.6469684951503</v>
       </c>
       <c r="O61">
-        <v>78.30696888546241</v>
+        <v>77.66468149369059</v>
       </c>
       <c r="P61">
-        <v>211.7188418014354</v>
+        <v>209.9822870014597</v>
       </c>
       <c r="Q61">
-        <v>258.8188418014353</v>
+        <v>257.0822870014597</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1471241756152394</v>
+        <v>0.1493237309916853</v>
       </c>
       <c r="T61">
-        <v>1.213837515116465</v>
+        <v>1.240187621754832</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6324,7 +6324,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.066421944091435</v>
+        <v>3.015314911689911</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,22 +6332,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08780529239667413</v>
+        <v>0.09115514279110012</v>
       </c>
       <c r="C62">
-        <v>1914.039916868474</v>
+        <v>1673.654193902</v>
       </c>
       <c r="D62">
-        <v>3808.825275758486</v>
+        <v>3605.550975440178</v>
       </c>
       <c r="E62">
-        <v>971.0430940733256</v>
+        <v>1008.154516721492</v>
       </c>
       <c r="F62">
-        <v>2226.685358890011</v>
+        <v>2263.796781538178</v>
       </c>
       <c r="G62">
         <v>331.9</v>
@@ -6368,45 +6368,45 @@
         <v>430.3775</v>
       </c>
       <c r="M62">
-        <v>142.7305315048497</v>
+        <v>162.766988592595</v>
       </c>
       <c r="N62">
-        <v>287.6469684951503</v>
+        <v>267.6105114074049</v>
       </c>
       <c r="O62">
-        <v>77.66468149369059</v>
+        <v>72.25483807999935</v>
       </c>
       <c r="P62">
-        <v>209.9822870014597</v>
+        <v>195.3556733274056</v>
       </c>
       <c r="Q62">
-        <v>257.0822870014597</v>
+        <v>242.4556733274056</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1493237309916853</v>
+        <v>0.1516360840797439</v>
       </c>
       <c r="T62">
-        <v>1.240187621754832</v>
+        <v>1.267889015913116</v>
       </c>
       <c r="U62">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V62">
         <v>0.27</v>
       </c>
       <c r="W62">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.015314911689911</v>
+        <v>2.644132595444355</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,22 +6414,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09115514279110012</v>
+        <v>0.09108859318552612</v>
       </c>
       <c r="C63">
-        <v>1673.654193902</v>
+        <v>1640.369642466126</v>
       </c>
       <c r="D63">
-        <v>3605.550975440178</v>
+        <v>3609.37784665247</v>
       </c>
       <c r="E63">
-        <v>1008.154516721492</v>
+        <v>1045.265939369659</v>
       </c>
       <c r="F63">
-        <v>2263.796781538178</v>
+        <v>2300.908204186345</v>
       </c>
       <c r="G63">
         <v>331.9</v>
@@ -6450,28 +6450,28 @@
         <v>430.3775</v>
       </c>
       <c r="M63">
-        <v>162.766988592595</v>
+        <v>165.4352998809982</v>
       </c>
       <c r="N63">
-        <v>267.6105114074049</v>
+        <v>264.9422001190018</v>
       </c>
       <c r="O63">
-        <v>72.25483807999935</v>
+        <v>71.53439403213048</v>
       </c>
       <c r="P63">
-        <v>195.3556733274056</v>
+        <v>193.4078060868713</v>
       </c>
       <c r="Q63">
-        <v>242.4556733274056</v>
+        <v>240.5078060868713</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1516360840797439</v>
+        <v>0.1540701399619108</v>
       </c>
       <c r="T63">
-        <v>1.267889015913116</v>
+        <v>1.297048378184994</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.644132595444355</v>
+        <v>2.601485295517833</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,22 +6496,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09108859318552612</v>
+        <v>0.09102204357995211</v>
       </c>
       <c r="C64">
-        <v>1640.369642466126</v>
+        <v>1607.0932232152</v>
       </c>
       <c r="D64">
-        <v>3609.37784665247</v>
+        <v>3613.212850049712</v>
       </c>
       <c r="E64">
-        <v>1045.265939369659</v>
+        <v>1082.377362017826</v>
       </c>
       <c r="F64">
-        <v>2300.908204186345</v>
+        <v>2338.019626834512</v>
       </c>
       <c r="G64">
         <v>331.9</v>
@@ -6532,28 +6532,28 @@
         <v>430.3775</v>
       </c>
       <c r="M64">
-        <v>165.4352998809982</v>
+        <v>168.1036111694014</v>
       </c>
       <c r="N64">
-        <v>264.9422001190018</v>
+        <v>262.2738888305986</v>
       </c>
       <c r="O64">
-        <v>71.53439403213048</v>
+        <v>70.81394998426163</v>
       </c>
       <c r="P64">
-        <v>193.4078060868713</v>
+        <v>191.459938846337</v>
       </c>
       <c r="Q64">
-        <v>240.5078060868713</v>
+        <v>238.5599388463369</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1540701399619108</v>
+        <v>0.156635766432303</v>
       </c>
       <c r="T64">
-        <v>1.297048378184994</v>
+        <v>1.327783922201297</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.601485295517833</v>
+        <v>2.560191878128661</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,22 +6578,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09102204357995211</v>
+        <v>0.0909554939743781</v>
       </c>
       <c r="C65">
-        <v>1607.0932232152</v>
+        <v>1573.8249620984</v>
       </c>
       <c r="D65">
-        <v>3613.212850049712</v>
+        <v>3617.056011581079</v>
       </c>
       <c r="E65">
-        <v>1082.377362017826</v>
+        <v>1119.488784665993</v>
       </c>
       <c r="F65">
-        <v>2338.019626834512</v>
+        <v>2375.131049482679</v>
       </c>
       <c r="G65">
         <v>331.9</v>
@@ -6614,28 +6614,28 @@
         <v>430.3775</v>
       </c>
       <c r="M65">
-        <v>168.1036111694014</v>
+        <v>170.7719224578046</v>
       </c>
       <c r="N65">
-        <v>262.2738888305986</v>
+        <v>259.6055775421954</v>
       </c>
       <c r="O65">
-        <v>70.81394998426163</v>
+        <v>70.09350593639276</v>
       </c>
       <c r="P65">
-        <v>191.459938846337</v>
+        <v>189.5120716058026</v>
       </c>
       <c r="Q65">
-        <v>238.5599388463369</v>
+        <v>236.6120716058026</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.156635766432303</v>
+        <v>0.1593439277066058</v>
       </c>
       <c r="T65">
-        <v>1.327783922201297</v>
+        <v>1.360226996440729</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.560191878128661</v>
+        <v>2.5201888800329</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,22 +6660,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0909554939743781</v>
+        <v>0.09273949436880408</v>
       </c>
       <c r="C66">
-        <v>1573.8249620984</v>
+        <v>1436.439166244672</v>
       </c>
       <c r="D66">
-        <v>3617.056011581079</v>
+        <v>3516.781638375518</v>
       </c>
       <c r="E66">
-        <v>1119.488784665993</v>
+        <v>1156.60020731416</v>
       </c>
       <c r="F66">
-        <v>2375.131049482679</v>
+        <v>2412.242472130846</v>
       </c>
       <c r="G66">
         <v>331.9</v>
@@ -6696,45 +6696,45 @@
         <v>430.3775</v>
       </c>
       <c r="M66">
-        <v>170.7719224578046</v>
+        <v>182.8479793875181</v>
       </c>
       <c r="N66">
-        <v>259.6055775421954</v>
+        <v>247.5295206124819</v>
       </c>
       <c r="O66">
-        <v>70.09350593639276</v>
+        <v>66.83297056537012</v>
       </c>
       <c r="P66">
-        <v>189.5120716058026</v>
+        <v>180.6965500471118</v>
       </c>
       <c r="Q66">
-        <v>236.6120716058026</v>
+        <v>227.7965500471117</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1593439277066058</v>
+        <v>0.162206841053726</v>
       </c>
       <c r="T66">
-        <v>1.360226996440729</v>
+        <v>1.394523960636699</v>
       </c>
       <c r="U66">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V66">
         <v>0.27</v>
       </c>
       <c r="W66">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.5201888800329</v>
+        <v>2.353744905695027</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,22 +6742,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09273949436880408</v>
+        <v>0.09270141476323007</v>
       </c>
       <c r="C67">
-        <v>1436.439166244672</v>
+        <v>1401.410002303177</v>
       </c>
       <c r="D67">
-        <v>3516.781638375518</v>
+        <v>3518.863897082189</v>
       </c>
       <c r="E67">
-        <v>1156.60020731416</v>
+        <v>1193.711629962327</v>
       </c>
       <c r="F67">
-        <v>2412.242472130846</v>
+        <v>2449.353894779013</v>
       </c>
       <c r="G67">
         <v>331.9</v>
@@ -6778,28 +6778,28 @@
         <v>430.3775</v>
       </c>
       <c r="M67">
-        <v>182.8479793875181</v>
+        <v>185.6610252242492</v>
       </c>
       <c r="N67">
-        <v>247.5295206124819</v>
+        <v>244.7164747757508</v>
       </c>
       <c r="O67">
-        <v>66.83297056537012</v>
+        <v>66.07344818945273</v>
       </c>
       <c r="P67">
-        <v>180.6965500471118</v>
+        <v>178.6430265862981</v>
       </c>
       <c r="Q67">
-        <v>227.7965500471117</v>
+        <v>225.7430265862981</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.162206841053726</v>
+        <v>0.1652381610683237</v>
       </c>
       <c r="T67">
-        <v>1.394523960636699</v>
+        <v>1.430838393314785</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.353744905695027</v>
+        <v>2.318082104093587</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,22 +6824,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09270141476323007</v>
+        <v>0.09266333515765607</v>
       </c>
       <c r="C68">
-        <v>1401.410002303177</v>
+        <v>1366.383305600472</v>
       </c>
       <c r="D68">
-        <v>3518.863897082189</v>
+        <v>3520.948623027651</v>
       </c>
       <c r="E68">
-        <v>1193.711629962327</v>
+        <v>1230.823052610494</v>
       </c>
       <c r="F68">
-        <v>2449.353894779013</v>
+        <v>2486.465317427179</v>
       </c>
       <c r="G68">
         <v>331.9</v>
@@ -6860,28 +6860,28 @@
         <v>430.3775</v>
       </c>
       <c r="M68">
-        <v>185.6610252242492</v>
+        <v>188.4740710609802</v>
       </c>
       <c r="N68">
-        <v>244.7164747757508</v>
+        <v>241.9034289390198</v>
       </c>
       <c r="O68">
-        <v>66.07344818945273</v>
+        <v>65.31392581353535</v>
       </c>
       <c r="P68">
-        <v>178.6430265862981</v>
+        <v>176.5895031254844</v>
       </c>
       <c r="Q68">
-        <v>225.7430265862981</v>
+        <v>223.6895031254844</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1652381610683237</v>
+        <v>0.1684531974474426</v>
       </c>
       <c r="T68">
-        <v>1.430838393314785</v>
+        <v>1.469353700700634</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6898,7 +6898,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.318082104093587</v>
+        <v>2.283483863733981</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,22 +6906,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09266333515765607</v>
+        <v>0.09262525555208206</v>
       </c>
       <c r="C69">
-        <v>1366.383305600472</v>
+        <v>1331.359080524249</v>
       </c>
       <c r="D69">
-        <v>3520.948623027651</v>
+        <v>3523.035820599595</v>
       </c>
       <c r="E69">
-        <v>1230.823052610494</v>
+        <v>1267.934475258661</v>
       </c>
       <c r="F69">
-        <v>2486.465317427179</v>
+        <v>2523.576740075346</v>
       </c>
       <c r="G69">
         <v>331.9</v>
@@ -6942,28 +6942,28 @@
         <v>430.3775</v>
       </c>
       <c r="M69">
-        <v>188.4740710609802</v>
+        <v>191.2871168977113</v>
       </c>
       <c r="N69">
-        <v>241.9034289390198</v>
+        <v>239.0903831022887</v>
       </c>
       <c r="O69">
-        <v>65.31392581353535</v>
+        <v>64.55440343761796</v>
       </c>
       <c r="P69">
-        <v>176.5895031254844</v>
+        <v>174.5359796646708</v>
       </c>
       <c r="Q69">
-        <v>223.6895031254844</v>
+        <v>221.6359796646707</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1684531974474426</v>
+        <v>0.1718691736002564</v>
       </c>
       <c r="T69">
-        <v>1.469353700700634</v>
+        <v>1.510276214798099</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.283483863733981</v>
+        <v>2.249903218679069</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,22 +6988,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09262525555208206</v>
+        <v>0.09258717594650803</v>
       </c>
       <c r="C70">
-        <v>1331.359080524249</v>
+        <v>1296.337331472616</v>
       </c>
       <c r="D70">
-        <v>3523.035820599595</v>
+        <v>3525.125494196129</v>
       </c>
       <c r="E70">
-        <v>1267.934475258661</v>
+        <v>1305.045897906827</v>
       </c>
       <c r="F70">
-        <v>2523.576740075346</v>
+        <v>2560.688162723513</v>
       </c>
       <c r="G70">
         <v>331.9</v>
@@ -7024,28 +7024,28 @@
         <v>430.3775</v>
       </c>
       <c r="M70">
-        <v>191.2871168977113</v>
+        <v>194.1001627344423</v>
       </c>
       <c r="N70">
-        <v>239.0903831022887</v>
+        <v>236.2773372655577</v>
       </c>
       <c r="O70">
-        <v>64.55440343761796</v>
+        <v>63.79488106170058</v>
       </c>
       <c r="P70">
-        <v>174.5359796646708</v>
+        <v>172.4824562038571</v>
       </c>
       <c r="Q70">
-        <v>221.6359796646707</v>
+        <v>219.5824562038571</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1718691736002564</v>
+        <v>0.1755055353113163</v>
       </c>
       <c r="T70">
-        <v>1.510276214798099</v>
+        <v>1.5538388910954</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.249903218679069</v>
+        <v>2.217295925654735</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,22 +7070,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09258717594650803</v>
+        <v>0.09254909634093403</v>
       </c>
       <c r="C71">
-        <v>1296.337331472616</v>
+        <v>1261.318062854113</v>
       </c>
       <c r="D71">
-        <v>3525.125494196129</v>
+        <v>3527.217648225793</v>
       </c>
       <c r="E71">
-        <v>1305.045897906827</v>
+        <v>1342.157320554995</v>
       </c>
       <c r="F71">
-        <v>2560.688162723513</v>
+        <v>2597.79958537168</v>
       </c>
       <c r="G71">
         <v>331.9</v>
@@ -7106,28 +7106,28 @@
         <v>430.3775</v>
       </c>
       <c r="M71">
-        <v>194.1001627344423</v>
+        <v>196.9132085711734</v>
       </c>
       <c r="N71">
-        <v>236.2773372655577</v>
+        <v>233.4642914288266</v>
       </c>
       <c r="O71">
-        <v>63.79488106170058</v>
+        <v>63.03535868578319</v>
       </c>
       <c r="P71">
-        <v>172.4824562038571</v>
+        <v>170.4289327430434</v>
       </c>
       <c r="Q71">
-        <v>219.5824562038571</v>
+        <v>217.5289327430434</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1755055353113163</v>
+        <v>0.1793843211364468</v>
       </c>
       <c r="T71">
-        <v>1.5538388910954</v>
+        <v>1.600305745812521</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.217295925654735</v>
+        <v>2.185620269573953</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,22 +7152,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09254909634093403</v>
+        <v>0.09251101673536002</v>
       </c>
       <c r="C72">
-        <v>1261.318062854113</v>
+        <v>1226.301279087759</v>
       </c>
       <c r="D72">
-        <v>3527.217648225793</v>
+        <v>3529.312287107606</v>
       </c>
       <c r="E72">
-        <v>1342.157320554995</v>
+        <v>1379.268743203161</v>
       </c>
       <c r="F72">
-        <v>2597.79958537168</v>
+        <v>2634.911008019847</v>
       </c>
       <c r="G72">
         <v>331.9</v>
@@ -7188,28 +7188,28 @@
         <v>430.3775</v>
       </c>
       <c r="M72">
-        <v>196.9132085711734</v>
+        <v>199.7262544079044</v>
       </c>
       <c r="N72">
-        <v>233.4642914288266</v>
+        <v>230.6512455920956</v>
       </c>
       <c r="O72">
-        <v>63.03535868578319</v>
+        <v>62.27583630986581</v>
       </c>
       <c r="P72">
-        <v>170.4289327430434</v>
+        <v>168.3754092822298</v>
       </c>
       <c r="Q72">
-        <v>217.5289327430434</v>
+        <v>215.4754092822297</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1793843211364468</v>
+        <v>0.183530609432276</v>
       </c>
       <c r="T72">
-        <v>1.600305745812521</v>
+        <v>1.649977211199789</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.185620269573953</v>
+        <v>2.154836885495446</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,22 +7234,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09251101673536002</v>
+        <v>0.09247293712978602</v>
       </c>
       <c r="C73">
-        <v>1226.301279087759</v>
+        <v>1191.286984603076</v>
       </c>
       <c r="D73">
-        <v>3529.312287107606</v>
+        <v>3531.40941527109</v>
       </c>
       <c r="E73">
-        <v>1379.268743203161</v>
+        <v>1416.380165851328</v>
       </c>
       <c r="F73">
-        <v>2634.911008019847</v>
+        <v>2672.022430668013</v>
       </c>
       <c r="G73">
         <v>331.9</v>
@@ -7270,28 +7270,28 @@
         <v>430.3775</v>
       </c>
       <c r="M73">
-        <v>199.7262544079044</v>
+        <v>202.5393002446354</v>
       </c>
       <c r="N73">
-        <v>230.6512455920956</v>
+        <v>227.8381997553646</v>
       </c>
       <c r="O73">
-        <v>62.27583630986582</v>
+        <v>61.51631393394844</v>
       </c>
       <c r="P73">
-        <v>168.3754092822298</v>
+        <v>166.3218858214161</v>
       </c>
       <c r="Q73">
-        <v>215.4754092822297</v>
+        <v>213.4218858214161</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1835306094322759</v>
+        <v>0.1879730611778072</v>
       </c>
       <c r="T73">
-        <v>1.649977211199788</v>
+        <v>1.703196638400432</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7308,7 +7308,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.154836885495447</v>
+        <v>2.124908595419122</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,22 +7316,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09247293712978602</v>
+        <v>0.092434857524212</v>
       </c>
       <c r="C74">
-        <v>1191.286984603076</v>
+        <v>1156.275183840117</v>
       </c>
       <c r="D74">
-        <v>3531.40941527109</v>
+        <v>3533.509037156297</v>
       </c>
       <c r="E74">
-        <v>1416.380165851328</v>
+        <v>1453.491588499495</v>
       </c>
       <c r="F74">
-        <v>2672.022430668013</v>
+        <v>2709.13385331618</v>
       </c>
       <c r="G74">
         <v>331.9</v>
@@ -7352,28 +7352,28 @@
         <v>430.3775</v>
       </c>
       <c r="M74">
-        <v>202.5393002446354</v>
+        <v>205.3523460813665</v>
       </c>
       <c r="N74">
-        <v>227.8381997553646</v>
+        <v>225.0251539186335</v>
       </c>
       <c r="O74">
-        <v>61.51631393394844</v>
+        <v>60.75679155803105</v>
       </c>
       <c r="P74">
-        <v>166.3218858214161</v>
+        <v>164.2683623606025</v>
       </c>
       <c r="Q74">
-        <v>213.4218858214161</v>
+        <v>211.3683623606024</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1879730611778072</v>
+        <v>0.1927445834230074</v>
       </c>
       <c r="T74">
-        <v>1.703196638400432</v>
+        <v>1.760358245393715</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7390,7 +7390,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.124908595419122</v>
+        <v>2.095800258495572</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,22 +7398,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.092434857524212</v>
+        <v>0.092396777918638</v>
       </c>
       <c r="C75">
-        <v>1156.275183840117</v>
+        <v>1121.265881249502</v>
       </c>
       <c r="D75">
-        <v>3533.509037156297</v>
+        <v>3535.611157213849</v>
       </c>
       <c r="E75">
-        <v>1453.491588499495</v>
+        <v>1490.603011147661</v>
       </c>
       <c r="F75">
-        <v>2709.13385331618</v>
+        <v>2746.245275964347</v>
       </c>
       <c r="G75">
         <v>331.9</v>
@@ -7434,28 +7434,28 @@
         <v>430.3775</v>
       </c>
       <c r="M75">
-        <v>205.3523460813665</v>
+        <v>208.1653919180975</v>
       </c>
       <c r="N75">
-        <v>225.0251539186335</v>
+        <v>222.2121080819025</v>
       </c>
       <c r="O75">
-        <v>60.75679155803105</v>
+        <v>59.99726918211367</v>
       </c>
       <c r="P75">
-        <v>164.2683623606025</v>
+        <v>162.2148388997888</v>
       </c>
       <c r="Q75">
-        <v>211.3683623606024</v>
+        <v>209.3148388997888</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1927445834230074</v>
+        <v>0.1978831458409153</v>
       </c>
       <c r="T75">
-        <v>1.760358245393715</v>
+        <v>1.82191689907879</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.095800258495572</v>
+        <v>2.067478633380767</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,22 +7480,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.092396777918638</v>
+        <v>0.09235869831306398</v>
       </c>
       <c r="C76">
-        <v>1121.265881249502</v>
+        <v>1086.25908129245</v>
       </c>
       <c r="D76">
-        <v>3535.611157213849</v>
+        <v>3537.715779904965</v>
       </c>
       <c r="E76">
-        <v>1490.603011147661</v>
+        <v>1527.714433795829</v>
       </c>
       <c r="F76">
-        <v>2746.245275964347</v>
+        <v>2783.356698612514</v>
       </c>
       <c r="G76">
         <v>331.9</v>
@@ -7516,28 +7516,28 @@
         <v>430.3775</v>
       </c>
       <c r="M76">
-        <v>208.1653919180975</v>
+        <v>210.9784377548286</v>
       </c>
       <c r="N76">
-        <v>222.2121080819025</v>
+        <v>219.3990622451714</v>
       </c>
       <c r="O76">
-        <v>59.99726918211367</v>
+        <v>59.23774680619628</v>
       </c>
       <c r="P76">
-        <v>162.2148388997888</v>
+        <v>160.1613154389751</v>
       </c>
       <c r="Q76">
-        <v>209.3148388997888</v>
+        <v>207.2613154389751</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1978831458409153</v>
+        <v>0.2034327932522559</v>
       </c>
       <c r="T76">
-        <v>1.82191689907879</v>
+        <v>1.888400245058671</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.067478633380767</v>
+        <v>2.039912251602356</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,22 +7562,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09235869831306398</v>
+        <v>0.09232061870748998</v>
       </c>
       <c r="C77">
-        <v>1086.25908129245</v>
+        <v>1051.254788440806</v>
       </c>
       <c r="D77">
-        <v>3537.715779904965</v>
+        <v>3539.822909701487</v>
       </c>
       <c r="E77">
-        <v>1527.714433795829</v>
+        <v>1564.825856443995</v>
       </c>
       <c r="F77">
-        <v>2783.356698612514</v>
+        <v>2820.468121260681</v>
       </c>
       <c r="G77">
         <v>331.9</v>
@@ -7598,28 +7598,28 @@
         <v>430.3775</v>
       </c>
       <c r="M77">
-        <v>210.9784377548286</v>
+        <v>213.7914835915597</v>
       </c>
       <c r="N77">
-        <v>219.3990622451714</v>
+        <v>216.5860164084403</v>
       </c>
       <c r="O77">
-        <v>59.23774680619628</v>
+        <v>58.4782244302789</v>
       </c>
       <c r="P77">
-        <v>160.1613154389751</v>
+        <v>158.1077919781615</v>
       </c>
       <c r="Q77">
-        <v>207.2613154389751</v>
+        <v>205.2077919781614</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2034327932522559</v>
+        <v>0.2094449112812083</v>
       </c>
       <c r="T77">
-        <v>1.888400245058671</v>
+        <v>1.960423869870209</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7636,7 +7636,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.039912251602356</v>
+        <v>2.013071300923378</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,22 +7644,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09232061870748998</v>
+        <v>0.1002643591019159</v>
       </c>
       <c r="C78">
-        <v>1051.254788440806</v>
+        <v>622.9251327370066</v>
       </c>
       <c r="D78">
-        <v>3539.822909701487</v>
+        <v>3148.604676645854</v>
       </c>
       <c r="E78">
-        <v>1564.825856443995</v>
+        <v>1601.937279092162</v>
       </c>
       <c r="F78">
-        <v>2820.468121260681</v>
+        <v>2857.579543908848</v>
       </c>
       <c r="G78">
         <v>331.9</v>
@@ -7680,45 +7680,45 @@
         <v>430.3775</v>
       </c>
       <c r="M78">
-        <v>213.7914835915597</v>
+        <v>257.1821589517963</v>
       </c>
       <c r="N78">
-        <v>216.5860164084403</v>
+        <v>173.1953410482037</v>
       </c>
       <c r="O78">
-        <v>58.4782244302789</v>
+        <v>46.76274208301501</v>
       </c>
       <c r="P78">
-        <v>158.1077919781615</v>
+        <v>126.4325989651887</v>
       </c>
       <c r="Q78">
-        <v>205.2077919781614</v>
+        <v>173.5325989651887</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2094449112812083</v>
+        <v>0.2159798221822433</v>
       </c>
       <c r="T78">
-        <v>1.960423869870209</v>
+        <v>2.038710418578402</v>
       </c>
       <c r="U78">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V78">
         <v>0.27</v>
       </c>
       <c r="W78">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.013071300923378</v>
+        <v>1.673434509431371</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,22 +7726,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1002643591019159</v>
+        <v>0.1003299394963419</v>
       </c>
       <c r="C79">
-        <v>622.9251327370066</v>
+        <v>582.9435336264273</v>
       </c>
       <c r="D79">
-        <v>3148.604676645854</v>
+        <v>3145.734500183442</v>
       </c>
       <c r="E79">
-        <v>1601.937279092162</v>
+        <v>1639.048701740329</v>
       </c>
       <c r="F79">
-        <v>2857.579543908848</v>
+        <v>2894.690966557015</v>
       </c>
       <c r="G79">
         <v>331.9</v>
@@ -7762,28 +7762,28 @@
         <v>430.3775</v>
       </c>
       <c r="M79">
-        <v>257.1821589517963</v>
+        <v>260.5221869901313</v>
       </c>
       <c r="N79">
-        <v>173.1953410482037</v>
+        <v>169.8553130098687</v>
       </c>
       <c r="O79">
-        <v>46.76274208301501</v>
+        <v>45.86093451266454</v>
       </c>
       <c r="P79">
-        <v>126.4325989651887</v>
+        <v>123.9943784972041</v>
       </c>
       <c r="Q79">
-        <v>173.5325989651887</v>
+        <v>171.0943784972041</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2159798221822433</v>
+        <v>0.2231088158924635</v>
       </c>
       <c r="T79">
-        <v>2.038710418578402</v>
+        <v>2.124113926260067</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7800,7 +7800,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.673434509431371</v>
+        <v>1.651980220848917</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,22 +7808,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1003299394963419</v>
+        <v>0.1003955198907679</v>
       </c>
       <c r="C80">
-        <v>582.9435336264273</v>
+        <v>542.9671624889784</v>
       </c>
       <c r="D80">
-        <v>3145.734500183442</v>
+        <v>3142.86955169416</v>
       </c>
       <c r="E80">
-        <v>1639.048701740329</v>
+        <v>1676.160124388496</v>
       </c>
       <c r="F80">
-        <v>2894.690966557015</v>
+        <v>2931.802389205181</v>
       </c>
       <c r="G80">
         <v>331.9</v>
@@ -7844,28 +7844,28 @@
         <v>430.3775</v>
       </c>
       <c r="M80">
-        <v>260.5221869901313</v>
+        <v>263.8622150284663</v>
       </c>
       <c r="N80">
-        <v>169.8553130098687</v>
+        <v>166.5152849715337</v>
       </c>
       <c r="O80">
-        <v>45.86093451266454</v>
+        <v>44.95912694231409</v>
       </c>
       <c r="P80">
-        <v>123.9943784972041</v>
+        <v>121.5561580292196</v>
       </c>
       <c r="Q80">
-        <v>171.0943784972041</v>
+        <v>168.6561580292195</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2231088158924635</v>
+        <v>0.2309167613846093</v>
       </c>
       <c r="T80">
-        <v>2.124113926260067</v>
+        <v>2.217651101339986</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.651980220848917</v>
+        <v>1.631069078812855</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,22 +7890,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1003955198907679</v>
+        <v>0.1004611002851939</v>
       </c>
       <c r="C81">
-        <v>542.9671624889784</v>
+        <v>502.9960050536729</v>
       </c>
       <c r="D81">
-        <v>3142.86955169416</v>
+        <v>3140.009816907021</v>
       </c>
       <c r="E81">
-        <v>1676.160124388496</v>
+        <v>1713.271547036663</v>
       </c>
       <c r="F81">
-        <v>2931.802389205181</v>
+        <v>2968.913811853348</v>
       </c>
       <c r="G81">
         <v>331.9</v>
@@ -7926,28 +7926,28 @@
         <v>430.3775</v>
       </c>
       <c r="M81">
-        <v>263.8622150284663</v>
+        <v>267.2022430668013</v>
       </c>
       <c r="N81">
-        <v>166.5152849715337</v>
+        <v>163.1752569331987</v>
       </c>
       <c r="O81">
-        <v>44.95912694231409</v>
+        <v>44.05731937196364</v>
       </c>
       <c r="P81">
-        <v>121.5561580292196</v>
+        <v>119.117937561235</v>
       </c>
       <c r="Q81">
-        <v>168.6561580292195</v>
+        <v>166.217937561235</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2309167613846093</v>
+        <v>0.2395055014259697</v>
       </c>
       <c r="T81">
-        <v>2.217651101339986</v>
+        <v>2.320541993927897</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7964,7 +7964,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.631069078812855</v>
+        <v>1.610680715327694</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,22 +7972,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1004611002851939</v>
+        <v>0.1005266806796199</v>
       </c>
       <c r="C82">
-        <v>502.9960050536729</v>
+        <v>463.0300471014161</v>
       </c>
       <c r="D82">
-        <v>3140.009816907021</v>
+        <v>3137.155281602932</v>
       </c>
       <c r="E82">
-        <v>1713.271547036663</v>
+        <v>1750.38296968483</v>
       </c>
       <c r="F82">
-        <v>2968.913811853348</v>
+        <v>3006.025234501516</v>
       </c>
       <c r="G82">
         <v>331.9</v>
@@ -8008,28 +8008,28 @@
         <v>430.3775</v>
       </c>
       <c r="M82">
-        <v>267.2022430668013</v>
+        <v>270.5422711051364</v>
       </c>
       <c r="N82">
-        <v>163.1752569331987</v>
+        <v>159.8352288948636</v>
       </c>
       <c r="O82">
-        <v>44.05731937196364</v>
+        <v>43.15551180161319</v>
       </c>
       <c r="P82">
-        <v>119.117937561235</v>
+        <v>116.6797170932504</v>
       </c>
       <c r="Q82">
-        <v>166.217937561235</v>
+        <v>163.7797170932504</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2395055014259697</v>
+        <v>0.2489983193664207</v>
       </c>
       <c r="T82">
-        <v>2.320541993927897</v>
+        <v>2.43426350678822</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.610680715327694</v>
+        <v>1.590795768224883</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,22 +8054,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1005266806796199</v>
+        <v>0.1005922610740459</v>
       </c>
       <c r="C83">
-        <v>463.0300471014161</v>
+        <v>423.0692744647768</v>
       </c>
       <c r="D83">
-        <v>3137.155281602932</v>
+        <v>3134.305931614459</v>
       </c>
       <c r="E83">
-        <v>1750.38296968483</v>
+        <v>1787.494392332997</v>
       </c>
       <c r="F83">
-        <v>3006.025234501516</v>
+        <v>3043.136657149682</v>
       </c>
       <c r="G83">
         <v>331.9</v>
@@ -8090,28 +8090,28 @@
         <v>430.3775</v>
       </c>
       <c r="M83">
-        <v>270.5422711051364</v>
+        <v>273.8822991434714</v>
       </c>
       <c r="N83">
-        <v>159.8352288948636</v>
+        <v>156.4952008565286</v>
       </c>
       <c r="O83">
-        <v>43.15551180161319</v>
+        <v>42.25370423126272</v>
       </c>
       <c r="P83">
-        <v>116.6797170932504</v>
+        <v>114.2414966252659</v>
       </c>
       <c r="Q83">
-        <v>163.7797170932504</v>
+        <v>161.3414966252658</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2489983193664207</v>
+        <v>0.2595458948558107</v>
       </c>
       <c r="T83">
-        <v>2.43426350678822</v>
+        <v>2.560620743299689</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.590795768224883</v>
+        <v>1.571395819831896</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,22 +8136,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1005922610740459</v>
+        <v>0.1006578414684719</v>
       </c>
       <c r="C84">
-        <v>423.0692744647768</v>
+        <v>383.1136730277426</v>
       </c>
       <c r="D84">
-        <v>3134.305931614459</v>
+        <v>3131.461752825592</v>
       </c>
       <c r="E84">
-        <v>1787.494392332997</v>
+        <v>1824.605814981164</v>
       </c>
       <c r="F84">
-        <v>3043.136657149682</v>
+        <v>3080.248079797849</v>
       </c>
       <c r="G84">
         <v>331.9</v>
@@ -8172,28 +8172,28 @@
         <v>430.3775</v>
       </c>
       <c r="M84">
-        <v>273.8822991434714</v>
+        <v>277.2223271818064</v>
       </c>
       <c r="N84">
-        <v>156.4952008565286</v>
+        <v>153.1551728181936</v>
       </c>
       <c r="O84">
-        <v>42.25370423126272</v>
+        <v>41.35189666091227</v>
       </c>
       <c r="P84">
-        <v>114.2414966252659</v>
+        <v>111.8032761572813</v>
       </c>
       <c r="Q84">
-        <v>161.3414966252658</v>
+        <v>158.9032761572813</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2595458948558107</v>
+        <v>0.2713343615792466</v>
       </c>
       <c r="T84">
-        <v>2.560620743299689</v>
+        <v>2.701843537047803</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.571395819831896</v>
+        <v>1.552463340074886</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,22 +8218,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1006578414684719</v>
+        <v>0.1007234218628979</v>
       </c>
       <c r="C85">
-        <v>383.1136730277426</v>
+        <v>343.1632287254961</v>
       </c>
       <c r="D85">
-        <v>3131.461752825592</v>
+        <v>3128.622731171512</v>
       </c>
       <c r="E85">
-        <v>1824.605814981164</v>
+        <v>1861.71723762933</v>
       </c>
       <c r="F85">
-        <v>3080.248079797849</v>
+        <v>3117.359502446016</v>
       </c>
       <c r="G85">
         <v>331.9</v>
@@ -8254,28 +8254,28 @@
         <v>430.3775</v>
       </c>
       <c r="M85">
-        <v>277.2223271818064</v>
+        <v>280.5623552201415</v>
       </c>
       <c r="N85">
-        <v>153.1551728181936</v>
+        <v>149.8151447798585</v>
       </c>
       <c r="O85">
-        <v>41.35189666091227</v>
+        <v>40.45008909056181</v>
       </c>
       <c r="P85">
-        <v>111.8032761572813</v>
+        <v>109.3650556892967</v>
       </c>
       <c r="Q85">
-        <v>158.9032761572813</v>
+        <v>156.4650556892967</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2713343615792466</v>
+        <v>0.284596386643112</v>
       </c>
       <c r="T85">
-        <v>2.701843537047803</v>
+        <v>2.860719180014431</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.552463340074886</v>
+        <v>1.533981633645423</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,22 +8300,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1007234218628979</v>
+        <v>0.1007890022573239</v>
       </c>
       <c r="C86">
-        <v>343.1632287254965</v>
+        <v>303.2179275441772</v>
       </c>
       <c r="D86">
-        <v>3128.622731171512</v>
+        <v>3125.788852638359</v>
       </c>
       <c r="E86">
-        <v>1861.71723762933</v>
+        <v>1898.828660277497</v>
       </c>
       <c r="F86">
-        <v>3117.359502446016</v>
+        <v>3154.470925094182</v>
       </c>
       <c r="G86">
         <v>331.9</v>
@@ -8336,28 +8336,28 @@
         <v>430.3775</v>
       </c>
       <c r="M86">
-        <v>280.5623552201414</v>
+        <v>283.9023832584764</v>
       </c>
       <c r="N86">
-        <v>149.8151447798586</v>
+        <v>146.4751167415236</v>
       </c>
       <c r="O86">
-        <v>40.45008909056182</v>
+        <v>39.54828152021138</v>
       </c>
       <c r="P86">
-        <v>109.3650556892968</v>
+        <v>106.9268352213122</v>
       </c>
       <c r="Q86">
-        <v>156.4650556892967</v>
+        <v>154.0268352213122</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2845963866431118</v>
+        <v>0.2996266817154926</v>
       </c>
       <c r="T86">
-        <v>2.860719180014429</v>
+        <v>3.040778242043273</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8374,7 +8374,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.533981633645423</v>
+        <v>1.515934790896654</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,22 +8382,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1007890022573239</v>
+        <v>0.1402231583951598</v>
       </c>
       <c r="C87">
-        <v>303.2179275441772</v>
+        <v>-836.0744922024128</v>
       </c>
       <c r="D87">
-        <v>3125.788852638359</v>
+        <v>2023.607855539937</v>
       </c>
       <c r="E87">
-        <v>1898.828660277497</v>
+        <v>1935.940082925664</v>
       </c>
       <c r="F87">
-        <v>3154.470925094182</v>
+        <v>3191.582347742349</v>
       </c>
       <c r="G87">
         <v>331.9</v>
@@ -8418,45 +8418,45 @@
         <v>430.3775</v>
       </c>
       <c r="M87">
-        <v>283.9023832584764</v>
+        <v>468.5242886485769</v>
       </c>
       <c r="N87">
-        <v>146.4751167415236</v>
+        <v>-38.14678864857689</v>
       </c>
       <c r="O87">
-        <v>39.54828152021138</v>
+        <v>-10.29963293511576</v>
       </c>
       <c r="P87">
-        <v>106.9268352213122</v>
+        <v>-27.84715571346113</v>
       </c>
       <c r="Q87">
-        <v>154.0268352213122</v>
+        <v>19.25284428653884</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2996266817154926</v>
+        <v>0.3234770821509298</v>
       </c>
       <c r="T87">
-        <v>3.040778242043273</v>
+        <v>3.32649989359678</v>
       </c>
       <c r="U87">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.27</v>
+        <v>0.2480168644728659</v>
       </c>
       <c r="W87">
-        <v>0.06569999999999999</v>
+        <v>0.1103911242953833</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.515934790896654</v>
+        <v>0.918580979529133</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,22 +8464,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1402231583951598</v>
+        <v>0.1412331583951598</v>
       </c>
       <c r="C88">
-        <v>-836.0744922024128</v>
+        <v>-891.2978099686416</v>
       </c>
       <c r="D88">
-        <v>2023.607855539937</v>
+        <v>2005.495960421875</v>
       </c>
       <c r="E88">
-        <v>1935.940082925664</v>
+        <v>1973.051505573831</v>
       </c>
       <c r="F88">
-        <v>3191.582347742349</v>
+        <v>3228.693770390516</v>
       </c>
       <c r="G88">
         <v>331.9</v>
@@ -8500,37 +8500,37 @@
         <v>430.3775</v>
       </c>
       <c r="M88">
-        <v>468.5242886485769</v>
+        <v>473.9722454933279</v>
       </c>
       <c r="N88">
-        <v>-38.14678864857689</v>
+        <v>-43.59474549332788</v>
       </c>
       <c r="O88">
-        <v>-10.29963293511576</v>
+        <v>-11.77058128319853</v>
       </c>
       <c r="P88">
-        <v>-27.84715571346113</v>
+        <v>-31.82416421012935</v>
       </c>
       <c r="Q88">
-        <v>19.25284428653884</v>
+        <v>15.27583578987062</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3234770821509298</v>
+        <v>0.3448368577010014</v>
       </c>
       <c r="T88">
-        <v>3.32649989359678</v>
+        <v>3.582384500796532</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2480168644728659</v>
+        <v>0.2451660959157065</v>
       </c>
       <c r="W88">
-        <v>0.1103911242953833</v>
+        <v>0.1108096171195743</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.918580979529133</v>
+        <v>0.9080225774655796</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,22 +8546,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1412331583951598</v>
+        <v>0.1422431583951598</v>
       </c>
       <c r="C89">
-        <v>-891.2978099686416</v>
+        <v>-946.1997900540623</v>
       </c>
       <c r="D89">
-        <v>2005.495960421875</v>
+        <v>1987.705402984621</v>
       </c>
       <c r="E89">
-        <v>1973.051505573831</v>
+        <v>2010.162928221998</v>
       </c>
       <c r="F89">
-        <v>3228.693770390516</v>
+        <v>3265.805193038683</v>
       </c>
       <c r="G89">
         <v>331.9</v>
@@ -8582,37 +8582,37 @@
         <v>430.3775</v>
       </c>
       <c r="M89">
-        <v>473.9722454933279</v>
+        <v>479.4202023380788</v>
       </c>
       <c r="N89">
-        <v>-43.59474549332788</v>
+        <v>-49.04270233807875</v>
       </c>
       <c r="O89">
-        <v>-11.77058128319853</v>
+        <v>-13.24152963128127</v>
       </c>
       <c r="P89">
-        <v>-31.82416421012935</v>
+        <v>-35.80117270679749</v>
       </c>
       <c r="Q89">
-        <v>15.27583578987062</v>
+        <v>11.29882729320248</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3448368577010014</v>
+        <v>0.3697565958427515</v>
       </c>
       <c r="T89">
-        <v>3.582384500796532</v>
+        <v>3.880916542529577</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2451660959157065</v>
+        <v>0.242380117553028</v>
       </c>
       <c r="W89">
-        <v>0.1108096171195743</v>
+        <v>0.1112185987432155</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9080225774655796</v>
+        <v>0.8977041390852889</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,22 +8628,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1422431583951598</v>
+        <v>0.1432531583951598</v>
       </c>
       <c r="C90">
-        <v>-946.1997900540623</v>
+        <v>-1000.78890892963</v>
       </c>
       <c r="D90">
-        <v>1987.705402984621</v>
+        <v>1970.227706757219</v>
       </c>
       <c r="E90">
-        <v>2010.162928221998</v>
+        <v>2047.274350870164</v>
       </c>
       <c r="F90">
-        <v>3265.805193038683</v>
+        <v>3302.91661568685</v>
       </c>
       <c r="G90">
         <v>331.9</v>
@@ -8664,37 +8664,37 @@
         <v>430.3775</v>
       </c>
       <c r="M90">
-        <v>479.4202023380788</v>
+        <v>484.8681591828296</v>
       </c>
       <c r="N90">
-        <v>-49.04270233807875</v>
+        <v>-54.49065918282963</v>
       </c>
       <c r="O90">
-        <v>-13.24152963128127</v>
+        <v>-14.712477979364</v>
       </c>
       <c r="P90">
-        <v>-35.80117270679749</v>
+        <v>-39.77818120346563</v>
       </c>
       <c r="Q90">
-        <v>11.29882729320248</v>
+        <v>7.321818796534338</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3697565958427515</v>
+        <v>0.3992071954648198</v>
       </c>
       <c r="T90">
-        <v>3.880916542529577</v>
+        <v>4.233727137304993</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.242380117553028</v>
+        <v>0.2396567454456906</v>
       </c>
       <c r="W90">
-        <v>0.1112185987432155</v>
+        <v>0.1116183897685726</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8977041390852889</v>
+        <v>0.8876175757247801</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,22 +8710,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1432531583951598</v>
+        <v>0.1442631583951598</v>
       </c>
       <c r="C91">
-        <v>-1000.78890892963</v>
+        <v>-1055.073347533818</v>
       </c>
       <c r="D91">
-        <v>1970.227706757219</v>
+        <v>1953.054690801199</v>
       </c>
       <c r="E91">
-        <v>2047.274350870164</v>
+        <v>2084.385773518331</v>
       </c>
       <c r="F91">
-        <v>3302.91661568685</v>
+        <v>3340.028038335017</v>
       </c>
       <c r="G91">
         <v>331.9</v>
@@ -8746,37 +8746,37 @@
         <v>430.3775</v>
       </c>
       <c r="M91">
-        <v>484.8681591828296</v>
+        <v>490.3161160275805</v>
       </c>
       <c r="N91">
-        <v>-54.49065918282963</v>
+        <v>-59.93861602758051</v>
       </c>
       <c r="O91">
-        <v>-14.712477979364</v>
+        <v>-16.18342632744674</v>
       </c>
       <c r="P91">
-        <v>-39.77818120346563</v>
+        <v>-43.75518970013377</v>
       </c>
       <c r="Q91">
-        <v>7.321818796534338</v>
+        <v>3.344810299866197</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3992071954648198</v>
+        <v>0.4345479150113017</v>
       </c>
       <c r="T91">
-        <v>4.233727137304993</v>
+        <v>4.657099851035492</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2396567454456906</v>
+        <v>0.2369938927185163</v>
       </c>
       <c r="W91">
-        <v>0.1116183897685726</v>
+        <v>0.1120092965489218</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8876175757247801</v>
+        <v>0.877755158216727</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,22 +8792,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1442631583951598</v>
+        <v>0.1452731583951598</v>
       </c>
       <c r="C92">
-        <v>-1055.073347533818</v>
+        <v>-1109.061004041013</v>
       </c>
       <c r="D92">
-        <v>1953.054690801199</v>
+        <v>1936.17845694217</v>
       </c>
       <c r="E92">
-        <v>2084.385773518331</v>
+        <v>2121.497196166498</v>
       </c>
       <c r="F92">
-        <v>3340.028038335017</v>
+        <v>3377.139460983184</v>
       </c>
       <c r="G92">
         <v>331.9</v>
@@ -8828,37 +8828,37 @@
         <v>430.3775</v>
       </c>
       <c r="M92">
-        <v>490.3161160275805</v>
+        <v>495.7640728723314</v>
       </c>
       <c r="N92">
-        <v>-59.93861602758051</v>
+        <v>-65.38657287233139</v>
       </c>
       <c r="O92">
-        <v>-16.18342632744674</v>
+        <v>-17.65437467552947</v>
       </c>
       <c r="P92">
-        <v>-43.75518970013377</v>
+        <v>-47.73219819680191</v>
       </c>
       <c r="Q92">
-        <v>3.344810299866197</v>
+        <v>-0.6321981968019443</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4345479150113017</v>
+        <v>0.4777421277903354</v>
       </c>
       <c r="T92">
-        <v>4.657099851035492</v>
+        <v>5.174555390039437</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2369938927185163</v>
+        <v>0.2343895642271041</v>
       </c>
       <c r="W92">
-        <v>0.1120092965489218</v>
+        <v>0.1123916119714611</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.877755158216727</v>
+        <v>0.8681094971374224</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,22 +8874,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1452731583951598</v>
+        <v>0.1462831583951598</v>
       </c>
       <c r="C93">
-        <v>-1109.061004041013</v>
+        <v>-1162.7595059736</v>
       </c>
       <c r="D93">
-        <v>1936.17845694217</v>
+        <v>1919.59137765775</v>
       </c>
       <c r="E93">
-        <v>2121.497196166498</v>
+        <v>2158.608618814666</v>
       </c>
       <c r="F93">
-        <v>3377.139460983184</v>
+        <v>3414.250883631351</v>
       </c>
       <c r="G93">
         <v>331.9</v>
@@ -8910,37 +8910,37 @@
         <v>430.3775</v>
       </c>
       <c r="M93">
-        <v>495.7640728723314</v>
+        <v>501.2120297170824</v>
       </c>
       <c r="N93">
-        <v>-65.38657287233139</v>
+        <v>-70.83452971708238</v>
       </c>
       <c r="O93">
-        <v>-17.65437467552947</v>
+        <v>-19.12532302361224</v>
       </c>
       <c r="P93">
-        <v>-47.73219819680191</v>
+        <v>-51.70920669347014</v>
       </c>
       <c r="Q93">
-        <v>-0.6321981968019443</v>
+        <v>-4.609206693470171</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4777421277903354</v>
+        <v>0.5317348937641274</v>
       </c>
       <c r="T93">
-        <v>5.174555390039437</v>
+        <v>5.821374813794368</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2343895642271041</v>
+        <v>0.2318418515724616</v>
       </c>
       <c r="W93">
-        <v>0.1123916119714611</v>
+        <v>0.1127656161891626</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8681094971374224</v>
+        <v>0.8586735243424501</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,22 +8956,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1462831583951598</v>
+        <v>0.1472931583951598</v>
       </c>
       <c r="C94">
-        <v>-1162.7595059736</v>
+        <v>-1216.176221696749</v>
       </c>
       <c r="D94">
-        <v>1919.59137765775</v>
+        <v>1903.286084582769</v>
       </c>
       <c r="E94">
-        <v>2158.608618814666</v>
+        <v>2195.720041462832</v>
       </c>
       <c r="F94">
-        <v>3414.250883631351</v>
+        <v>3451.362306279518</v>
       </c>
       <c r="G94">
         <v>331.9</v>
@@ -8992,37 +8992,37 @@
         <v>430.3775</v>
       </c>
       <c r="M94">
-        <v>501.2120297170824</v>
+        <v>506.6599865618333</v>
       </c>
       <c r="N94">
-        <v>-70.83452971708238</v>
+        <v>-76.28248656183325</v>
       </c>
       <c r="O94">
-        <v>-19.12532302361224</v>
+        <v>-20.59627137169498</v>
       </c>
       <c r="P94">
-        <v>-51.70920669347014</v>
+        <v>-55.68621519013827</v>
       </c>
       <c r="Q94">
-        <v>-4.609206693470171</v>
+        <v>-8.586215190138304</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5317348937641274</v>
+        <v>0.60115416430186</v>
       </c>
       <c r="T94">
-        <v>5.821374813794368</v>
+        <v>6.652999787193565</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2318418515724616</v>
+        <v>0.2293489284372738</v>
       </c>
       <c r="W94">
-        <v>0.1127656161891626</v>
+        <v>0.1131315773054082</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8586735243424501</v>
+        <v>0.8494404756936067</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,22 +9038,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1472931583951598</v>
+        <v>0.1483031583951598</v>
       </c>
       <c r="C95">
-        <v>-1216.176221696749</v>
+        <v>-1269.31827133231</v>
       </c>
       <c r="D95">
-        <v>1903.286084582769</v>
+        <v>1887.255457595375</v>
       </c>
       <c r="E95">
-        <v>2195.720041462832</v>
+        <v>2232.831464110999</v>
       </c>
       <c r="F95">
-        <v>3451.362306279518</v>
+        <v>3488.473728927685</v>
       </c>
       <c r="G95">
         <v>331.9</v>
@@ -9074,37 +9074,37 @@
         <v>430.3775</v>
       </c>
       <c r="M95">
-        <v>506.6599865618333</v>
+        <v>512.1079434065841</v>
       </c>
       <c r="N95">
-        <v>-76.28248656183325</v>
+        <v>-81.73044340658413</v>
       </c>
       <c r="O95">
-        <v>-20.59627137169498</v>
+        <v>-22.06721971977772</v>
       </c>
       <c r="P95">
-        <v>-55.68621519013827</v>
+        <v>-59.66322368680641</v>
       </c>
       <c r="Q95">
-        <v>-8.586215190138304</v>
+        <v>-12.56322368680645</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.60115416430186</v>
+        <v>0.6937131916855035</v>
       </c>
       <c r="T95">
-        <v>6.652999787193565</v>
+        <v>7.761833085059162</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2293489284372738</v>
+        <v>0.226909046219856</v>
       </c>
       <c r="W95">
-        <v>0.1131315773054082</v>
+        <v>0.1134897520149252</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8494404756936067</v>
+        <v>0.8404038748883556</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,22 +9120,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1483031583951598</v>
+        <v>0.1493131583951598</v>
       </c>
       <c r="C96">
-        <v>-1269.31827133231</v>
+        <v>-1322.192537125778</v>
       </c>
       <c r="D96">
-        <v>1887.255457595375</v>
+        <v>1871.492614450073</v>
       </c>
       <c r="E96">
-        <v>2232.831464110999</v>
+        <v>2269.942886759166</v>
       </c>
       <c r="F96">
-        <v>3488.473728927685</v>
+        <v>3525.585151575851</v>
       </c>
       <c r="G96">
         <v>331.9</v>
@@ -9156,37 +9156,37 @@
         <v>430.3775</v>
       </c>
       <c r="M96">
-        <v>512.1079434065841</v>
+        <v>517.5559002513351</v>
       </c>
       <c r="N96">
-        <v>-81.73044340658413</v>
+        <v>-87.17840025133506</v>
       </c>
       <c r="O96">
-        <v>-22.06721971977772</v>
+        <v>-23.53816806786047</v>
       </c>
       <c r="P96">
-        <v>-59.66322368680641</v>
+        <v>-63.64023218347459</v>
       </c>
       <c r="Q96">
-        <v>-12.56322368680645</v>
+        <v>-16.54023218347463</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6937131916855035</v>
+        <v>0.8232958300226046</v>
       </c>
       <c r="T96">
-        <v>7.761833085059162</v>
+        <v>9.314199702070999</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.226909046219856</v>
+        <v>0.2245205299438575</v>
       </c>
       <c r="W96">
-        <v>0.1134897520149252</v>
+        <v>0.1138403862042417</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8404038748883556</v>
+        <v>0.8315575183105833</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,22 +9202,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1493131583951598</v>
+        <v>0.1503231583951598</v>
       </c>
       <c r="C97">
-        <v>-1322.192537125778</v>
+        <v>-1374.805673298027</v>
       </c>
       <c r="D97">
-        <v>1871.492614450073</v>
+        <v>1855.990900925992</v>
       </c>
       <c r="E97">
-        <v>2269.942886759166</v>
+        <v>2307.054309407333</v>
       </c>
       <c r="F97">
-        <v>3525.585151575851</v>
+        <v>3562.696574224018</v>
       </c>
       <c r="G97">
         <v>331.9</v>
@@ -9238,37 +9238,37 @@
         <v>430.3775</v>
       </c>
       <c r="M97">
-        <v>517.5559002513351</v>
+        <v>523.0038570960859</v>
       </c>
       <c r="N97">
-        <v>-87.17840025133506</v>
+        <v>-92.62635709608588</v>
       </c>
       <c r="O97">
-        <v>-23.53816806786047</v>
+        <v>-25.00911641594319</v>
       </c>
       <c r="P97">
-        <v>-63.64023218347459</v>
+        <v>-67.61724068014269</v>
       </c>
       <c r="Q97">
-        <v>-16.54023218347463</v>
+        <v>-20.51724068014272</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8232958300226046</v>
+        <v>1.017669787528256</v>
       </c>
       <c r="T97">
-        <v>9.314199702070999</v>
+        <v>11.64274962758875</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2245205299438575</v>
+        <v>0.222181774423609</v>
       </c>
       <c r="W97">
-        <v>0.1138403862042417</v>
+        <v>0.1141837155146142</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8315575183105833</v>
+        <v>0.8228954608281815</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,22 +9284,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1503231583951598</v>
+        <v>0.1513331583951598</v>
       </c>
       <c r="C98">
-        <v>-1374.805673298026</v>
+        <v>-1427.164115411452</v>
       </c>
       <c r="D98">
-        <v>1855.990900925992</v>
+        <v>1840.743881460732</v>
       </c>
       <c r="E98">
-        <v>2307.054309407332</v>
+        <v>2344.165732055499</v>
       </c>
       <c r="F98">
-        <v>3562.696574224018</v>
+        <v>3599.807996872185</v>
       </c>
       <c r="G98">
         <v>331.9</v>
@@ -9320,37 +9320,37 @@
         <v>430.3775</v>
       </c>
       <c r="M98">
-        <v>523.0038570960859</v>
+        <v>528.4518139408367</v>
       </c>
       <c r="N98">
-        <v>-92.62635709608588</v>
+        <v>-98.0743139408367</v>
       </c>
       <c r="O98">
-        <v>-25.00911641594319</v>
+        <v>-26.48006476402591</v>
       </c>
       <c r="P98">
-        <v>-67.61724068014269</v>
+        <v>-71.59424917681079</v>
       </c>
       <c r="Q98">
-        <v>-20.51724068014272</v>
+        <v>-24.49424917681083</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.017669787528254</v>
+        <v>1.341626383371005</v>
       </c>
       <c r="T98">
-        <v>11.64274962758872</v>
+        <v>15.52366617011829</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.222181774423609</v>
+        <v>0.2198912406666647</v>
       </c>
       <c r="W98">
-        <v>0.1141837155146142</v>
+        <v>0.1145199658701336</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8228954608281815</v>
+        <v>0.8144120024691283</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,22 +9366,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1513331583951598</v>
+        <v>0.1523431583951598</v>
       </c>
       <c r="C99">
-        <v>-1427.164115411452</v>
+        <v>-1479.274089278228</v>
       </c>
       <c r="D99">
-        <v>1840.743881460732</v>
+        <v>1825.745330242124</v>
       </c>
       <c r="E99">
-        <v>2344.165732055499</v>
+        <v>2381.277154703666</v>
       </c>
       <c r="F99">
-        <v>3599.807996872185</v>
+        <v>3636.919419520352</v>
       </c>
       <c r="G99">
         <v>331.9</v>
@@ -9402,37 +9402,37 @@
         <v>430.3775</v>
       </c>
       <c r="M99">
-        <v>528.4518139408367</v>
+        <v>533.8997707855876</v>
       </c>
       <c r="N99">
-        <v>-98.0743139408367</v>
+        <v>-103.5222707855876</v>
       </c>
       <c r="O99">
-        <v>-26.48006476402591</v>
+        <v>-27.95101311210867</v>
       </c>
       <c r="P99">
-        <v>-71.59424917681079</v>
+        <v>-75.57125767347897</v>
       </c>
       <c r="Q99">
-        <v>-24.49424917681083</v>
+        <v>-28.471257673479</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.341626383371005</v>
+        <v>1.989539575056507</v>
       </c>
       <c r="T99">
-        <v>15.52366617011829</v>
+        <v>23.28549925517745</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2198912406666647</v>
+        <v>0.2176474524965966</v>
       </c>
       <c r="W99">
-        <v>0.1145199658701336</v>
+        <v>0.1148493539734996</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8144120024691283</v>
+        <v>0.8061016759133207</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,22 +9448,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1523431583951598</v>
+        <v>0.2096475875307134</v>
       </c>
       <c r="C100">
-        <v>-1479.274089278228</v>
+        <v>-2093.586197089638</v>
       </c>
       <c r="D100">
-        <v>1825.745330242124</v>
+        <v>1248.54464507888</v>
       </c>
       <c r="E100">
-        <v>2381.277154703666</v>
+        <v>2418.388577351833</v>
       </c>
       <c r="F100">
-        <v>3636.919419520352</v>
+        <v>3674.030842168519</v>
       </c>
       <c r="G100">
         <v>331.9</v>
@@ -9484,129 +9484,47 @@
         <v>430.3775</v>
       </c>
       <c r="M100">
-        <v>533.8997707855876</v>
+        <v>737.7453931074385</v>
       </c>
       <c r="N100">
-        <v>-103.5222707855876</v>
+        <v>-307.3678931074385</v>
       </c>
       <c r="O100">
-        <v>-27.95101311210867</v>
+        <v>-82.98933113900841</v>
       </c>
       <c r="P100">
-        <v>-75.57125767347897</v>
+        <v>-224.3785619684301</v>
       </c>
       <c r="Q100">
-        <v>-28.471257673479</v>
+        <v>-177.2785619684302</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.989539575056507</v>
+        <v>4.216722063668375</v>
       </c>
       <c r="T100">
-        <v>23.28549925517745</v>
+        <v>49.96657157846347</v>
       </c>
       <c r="U100">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.2176474524965966</v>
+        <v>0.1575095230490682</v>
       </c>
       <c r="W100">
-        <v>0.1148493539734996</v>
+        <v>0.1691720877717471</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.8061016759133207</v>
+        <v>0.583368603885438</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2096475875307134</v>
-      </c>
-      <c r="C101">
-        <v>-2093.586197089638</v>
-      </c>
-      <c r="D101">
-        <v>1248.54464507888</v>
-      </c>
-      <c r="E101">
-        <v>2418.388577351833</v>
-      </c>
-      <c r="F101">
-        <v>3674.030842168519</v>
-      </c>
-      <c r="G101">
-        <v>331.9</v>
-      </c>
-      <c r="H101">
-        <v>2455.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>477.4775</v>
-      </c>
-      <c r="K101">
-        <v>47.09999999999997</v>
-      </c>
-      <c r="L101">
-        <v>430.3775</v>
-      </c>
-      <c r="M101">
-        <v>737.7453931074385</v>
-      </c>
-      <c r="N101">
-        <v>-307.3678931074385</v>
-      </c>
-      <c r="O101">
-        <v>-82.98933113900841</v>
-      </c>
-      <c r="P101">
-        <v>-224.3785619684301</v>
-      </c>
-      <c r="Q101">
-        <v>-177.2785619684302</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.216722063668375</v>
-      </c>
-      <c r="T101">
-        <v>49.96657157846347</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1575095230490682</v>
-      </c>
-      <c r="W101">
-        <v>0.1691720877717471</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.583368603885438</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
